--- a/Cafe 2M.xlsx
+++ b/Cafe 2M.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GHOST\OneDrive\سطح المكتب\cafe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FEA5FB1-FA53-49BF-9359-4D55E1B29EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A09ECF7-E548-4D73-A6BB-30CD71C67DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="199">
   <si>
     <t>المشتريات اليومية</t>
   </si>
@@ -642,6 +642,9 @@
   </si>
   <si>
     <t>كانت في المصاريف النثرية</t>
+  </si>
+  <si>
+    <t>لحد 30/6</t>
   </si>
 </sst>
 </file>
@@ -1075,6 +1078,9 @@
     <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1092,9 +1098,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1593,12 +1596,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
@@ -1993,16 +1996,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
@@ -2268,15 +2271,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
@@ -2341,7 +2344,7 @@
       </c>
       <c r="E5" s="43">
         <f>SUM(الرواتب!I6:I31)</f>
-        <v>71734</v>
+        <v>75459</v>
       </c>
       <c r="F5" s="43">
         <v>-15401</v>
@@ -2391,15 +2394,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -2902,16 +2905,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -3608,12 +3611,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="70" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
     </row>
     <row r="3" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -3937,18 +3940,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
@@ -3974,14 +3977,14 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="71" t="s">
         <v>192</v>
       </c>
-      <c r="G7" s="70"/>
+      <c r="G7" s="71"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
@@ -4686,31 +4689,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64"/>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
+      <c r="A1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
     </row>
     <row r="5" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -4746,10 +4749,10 @@
       <c r="K5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="66" t="s">
+      <c r="U5" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="V5" s="67"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
@@ -5090,7 +5093,7 @@
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
-      <c r="I18" s="71">
+      <c r="I18" s="64">
         <v>600</v>
       </c>
       <c r="J18" s="30"/>
@@ -5320,9 +5323,13 @@
       </c>
       <c r="G29" s="30"/>
       <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
+      <c r="I29" s="30">
+        <v>3725</v>
+      </c>
       <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
+      <c r="K29" s="30" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
@@ -5367,7 +5374,7 @@
     <row r="32" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I32" s="23">
         <f>SUM(I6:I31)</f>
-        <v>71734</v>
+        <v>75459</v>
       </c>
       <c r="J32" s="38" t="s">
         <v>191</v>
@@ -5416,12 +5423,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
     </row>
     <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -5902,16 +5909,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -6295,15 +6302,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">

--- a/Cafe 2M.xlsx
+++ b/Cafe 2M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GHOST\OneDrive\سطح المكتب\cafe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A09ECF7-E548-4D73-A6BB-30CD71C67DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB4191C-B042-41FA-8C93-CA6751DFC753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الموظفين" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="ملخص شهري" sheetId="13" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">الرواتب!$A$1:$K$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">الرواتب!$A$1:$K$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">المصروفات!$A$1:$D$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'تقفيلة اليوم'!$A$6:$J$42</definedName>
   </definedNames>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="199">
   <si>
     <t>المشتريات اليومية</t>
   </si>
@@ -651,7 +651,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -825,8 +825,16 @@
       <charset val="178"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -854,6 +862,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -931,11 +950,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1078,13 +1098,16 @@
     <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1094,15 +1117,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
@@ -1596,12 +1620,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
@@ -1996,16 +2020,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
@@ -2259,7 +2283,7 @@
   <sheetPr>
     <tabColor rgb="FF50A280"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -2271,15 +2295,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
@@ -2336,18 +2360,19 @@
         <v>246428</v>
       </c>
       <c r="C5" s="43">
-        <f>SUM('المشتريات اليومية'!G36)</f>
+        <f>SUM('المشتريات اليومية'!G37)</f>
         <v>163610</v>
       </c>
       <c r="D5" s="43">
         <v>29085</v>
       </c>
       <c r="E5" s="43">
-        <f>SUM(الرواتب!I6:I31)</f>
-        <v>75459</v>
+        <f>SUM(الرواتب!I6:I32)</f>
+        <v>79709</v>
       </c>
       <c r="F5" s="43">
-        <v>-15401</v>
+        <f>SUM(E21)</f>
+        <v>-25976</v>
       </c>
       <c r="G5" s="44"/>
     </row>
@@ -2364,6 +2389,18 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E16" s="1">
+        <f>SUM(C5:E5)</f>
+        <v>272404</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="1">
+        <f>SUM(B5-E16)</f>
+        <v>-25976</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2394,15 +2431,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -2891,7 +2928,7 @@
   <sheetPr>
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2905,16 +2942,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -3283,69 +3320,58 @@
       <c r="H22" s="14"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="48">
-        <v>46199</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>22</v>
-      </c>
+      <c r="A23" s="48"/>
+      <c r="B23" s="39"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="33">
+      <c r="G23" s="33"/>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="48">
+        <v>46199</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="33">
         <f>3920+3150</f>
         <v>7070</v>
       </c>
-      <c r="H23" s="14"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="48">
-        <v>46200</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="25">
-        <v>1635</v>
-      </c>
       <c r="H24" s="14"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="48">
-        <v>46201</v>
+        <v>46200</v>
       </c>
       <c r="B25" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
       <c r="G25" s="25">
-        <v>13425</v>
+        <v>1635</v>
       </c>
       <c r="H25" s="14"/>
-      <c r="L25" s="3"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="48">
         <v>46201</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="C26" s="30" t="s">
         <v>188</v>
@@ -3356,16 +3382,17 @@
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="25">
-        <v>5895</v>
+        <v>13425</v>
       </c>
       <c r="H26" s="14"/>
+      <c r="L26" s="3"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="48">
         <v>46201</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C27" s="30" t="s">
         <v>188</v>
@@ -3376,7 +3403,7 @@
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="25">
-        <v>225</v>
+        <v>5895</v>
       </c>
       <c r="H27" s="14"/>
     </row>
@@ -3396,7 +3423,7 @@
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="25">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="H28" s="14"/>
     </row>
@@ -3408,35 +3435,35 @@
         <v>111</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
       <c r="G29" s="25">
-        <v>925</v>
+        <v>50</v>
       </c>
       <c r="H29" s="14"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="48">
-        <v>46202</v>
+        <v>46201</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
       <c r="G30" s="25">
-        <v>450</v>
+        <v>925</v>
       </c>
       <c r="H30" s="14"/>
     </row>
@@ -3448,15 +3475,15 @@
         <v>18</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>188</v>
+        <v>118</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>102</v>
+        <v>189</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
       <c r="G31" s="25">
-        <v>8440</v>
+        <v>450</v>
       </c>
       <c r="H31" s="14"/>
     </row>
@@ -3468,15 +3495,15 @@
         <v>18</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
       <c r="G32" s="25">
-        <v>1046</v>
+        <v>8440</v>
       </c>
       <c r="H32" s="14"/>
     </row>
@@ -3488,39 +3515,39 @@
         <v>18</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
       <c r="G33" s="25">
-        <v>8000</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>119</v>
-      </c>
+        <v>1046</v>
+      </c>
+      <c r="H33" s="14"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="48">
-        <v>46203</v>
+        <v>46202</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="17"/>
       <c r="G34" s="25">
-        <v>1700</v>
-      </c>
-      <c r="H34" s="14"/>
+        <v>8000</v>
+      </c>
+      <c r="H34" s="28" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="48">
@@ -3530,45 +3557,55 @@
         <v>19</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
       <c r="G35" s="25">
+        <v>1700</v>
+      </c>
+      <c r="H35" s="14"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="48">
+        <v>46203</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="25">
         <v>350</v>
       </c>
-      <c r="H35" s="14"/>
-    </row>
-    <row r="36" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="59"/>
-      <c r="B36" s="29"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="60">
-        <f>SUM(G4:G35)</f>
-        <v>163610</v>
-      </c>
-      <c r="H36" s="38" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H36" s="14"/>
+    </row>
+    <row r="37" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="59"/>
-      <c r="B37" s="29" t="str">
-        <f t="shared" ref="B37:B39" si="0">IF(A37="","",TEXT(A37,"dddd"))</f>
-        <v/>
-      </c>
+      <c r="B37" s="29"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
+      <c r="G37" s="60">
+        <f>SUM(G4:G36)</f>
+        <v>163610</v>
+      </c>
+      <c r="H37" s="38" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="59"/>
-      <c r="B38" t="str">
-        <f t="shared" si="0"/>
+      <c r="B38" s="29" t="str">
+        <f t="shared" ref="B38:B40" si="0">IF(A38="","",TEXT(A38,"dddd"))</f>
         <v/>
       </c>
       <c r="E38" s="1"/>
@@ -3576,7 +3613,7 @@
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
+      <c r="A39" s="59"/>
       <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3584,6 +3621,16 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3611,12 +3658,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="66" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
     </row>
     <row r="3" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -3940,18 +3987,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
@@ -3977,14 +4024,14 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="71" t="s">
+      <c r="F7" s="67" t="s">
         <v>192</v>
       </c>
-      <c r="G7" s="71"/>
+      <c r="G7" s="67"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
     </row>
     <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
@@ -4667,7 +4714,7 @@
     <tabColor rgb="FF808080"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4680,6 +4727,7 @@
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="12.140625" customWidth="1"/>
     <col min="11" max="11" width="21.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
     <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -4689,31 +4737,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65"/>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
+      <c r="A1" s="64"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
     </row>
     <row r="5" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -4749,10 +4797,10 @@
       <c r="K5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="67" t="s">
+      <c r="U5" s="68" t="s">
         <v>143</v>
       </c>
-      <c r="V5" s="68"/>
+      <c r="V5" s="69"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
@@ -4903,7 +4951,7 @@
       <c r="F11" s="41"/>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
-      <c r="I11" s="30">
+      <c r="I11" s="72">
         <v>2750</v>
       </c>
       <c r="J11" s="30"/>
@@ -4933,7 +4981,7 @@
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
-      <c r="I12" s="30">
+      <c r="I12" s="72">
         <v>3000</v>
       </c>
       <c r="J12" s="30">
@@ -5093,7 +5141,7 @@
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
-      <c r="I18" s="64">
+      <c r="I18" s="71">
         <v>600</v>
       </c>
       <c r="J18" s="30"/>
@@ -5114,7 +5162,7 @@
       <c r="F19" s="41"/>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
-      <c r="I19" s="30">
+      <c r="I19" s="72">
         <v>1000</v>
       </c>
       <c r="J19" s="30"/>
@@ -5136,100 +5184,97 @@
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
       <c r="I20" s="30">
-        <v>6000</v>
+        <f>6000+1500</f>
+        <v>7500</v>
       </c>
       <c r="J20" s="30"/>
       <c r="K20" s="30"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="14">
-        <v>16</v>
-      </c>
+      <c r="A21" s="14"/>
       <c r="B21" s="30" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C21" s="30"/>
       <c r="D21" s="25"/>
       <c r="E21" s="26"/>
-      <c r="F21" s="41">
-        <v>120</v>
-      </c>
+      <c r="F21" s="41"/>
       <c r="G21" s="26"/>
       <c r="H21" s="26"/>
-      <c r="I21" s="30"/>
+      <c r="I21" s="30">
+        <v>2750</v>
+      </c>
       <c r="J21" s="30"/>
       <c r="K21" s="30"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
+        <v>16</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="41">
+        <v>120</v>
+      </c>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="14">
         <v>17</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B23" s="30" t="s">
         <v>106</v>
-      </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="39">
-        <v>130</v>
-      </c>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30">
-        <v>1330</v>
-      </c>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>18</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>146</v>
       </c>
       <c r="C23" s="30"/>
       <c r="D23" s="28"/>
       <c r="E23" s="30"/>
       <c r="F23" s="39">
-        <f>500</f>
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="G23" s="30"/>
       <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
+      <c r="I23" s="30">
+        <v>1330</v>
+      </c>
       <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
+      <c r="K23" s="30" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="14">
-        <v>19</v>
+      <c r="A24">
+        <v>18</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="28"/>
       <c r="E24" s="30"/>
-      <c r="F24" s="39"/>
+      <c r="F24" s="39">
+        <f>500</f>
+        <v>500</v>
+      </c>
       <c r="G24" s="30"/>
       <c r="H24" s="30"/>
-      <c r="I24" s="30">
-        <v>1665</v>
-      </c>
+      <c r="I24" s="30"/>
       <c r="J24" s="30"/>
-      <c r="K24" s="30" t="s">
-        <v>143</v>
-      </c>
+      <c r="K24" s="30"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="28"/>
@@ -5238,7 +5283,7 @@
       <c r="G25" s="30"/>
       <c r="H25" s="30"/>
       <c r="I25" s="30">
-        <v>300</v>
+        <v>1665</v>
       </c>
       <c r="J25" s="30"/>
       <c r="K25" s="30" t="s">
@@ -5247,10 +5292,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C26" s="30"/>
       <c r="D26" s="28"/>
@@ -5259,7 +5304,7 @@
       <c r="G26" s="30"/>
       <c r="H26" s="30"/>
       <c r="I26" s="30">
-        <v>4104</v>
+        <v>300</v>
       </c>
       <c r="J26" s="30"/>
       <c r="K26" s="30" t="s">
@@ -5268,10 +5313,10 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C27" s="30"/>
       <c r="D27" s="28"/>
@@ -5280,7 +5325,7 @@
       <c r="G27" s="30"/>
       <c r="H27" s="30"/>
       <c r="I27" s="30">
-        <v>1290</v>
+        <v>4104</v>
       </c>
       <c r="J27" s="30"/>
       <c r="K27" s="30" t="s">
@@ -5289,10 +5334,10 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C28" s="30"/>
       <c r="D28" s="28"/>
@@ -5301,7 +5346,7 @@
       <c r="G28" s="30"/>
       <c r="H28" s="30"/>
       <c r="I28" s="30">
-        <v>2000</v>
+        <v>1290</v>
       </c>
       <c r="J28" s="30"/>
       <c r="K28" s="30" t="s">
@@ -5310,84 +5355,105 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C29" s="30"/>
       <c r="D29" s="28"/>
       <c r="E29" s="30"/>
-      <c r="F29" s="39">
-        <v>120</v>
-      </c>
+      <c r="F29" s="39"/>
       <c r="G29" s="30"/>
       <c r="H29" s="30"/>
       <c r="I29" s="30">
-        <v>3725</v>
+        <v>2000</v>
       </c>
       <c r="J29" s="30"/>
       <c r="K29" s="30" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C30" s="30"/>
       <c r="D30" s="28"/>
       <c r="E30" s="30"/>
-      <c r="F30" s="39"/>
+      <c r="F30" s="39">
+        <v>120</v>
+      </c>
       <c r="G30" s="30"/>
       <c r="H30" s="30"/>
       <c r="I30" s="30">
-        <v>4000</v>
+        <v>3725</v>
       </c>
       <c r="J30" s="30"/>
       <c r="K30" s="30" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <v>25</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" s="30"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30">
+        <v>4000</v>
+      </c>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="14">
+    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
         <v>26</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B32" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="30">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="30">
         <v>1500</v>
       </c>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-    </row>
-    <row r="32" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I32" s="23">
-        <f>SUM(I6:I31)</f>
-        <v>75459</v>
-      </c>
-      <c r="J32" s="38" t="s">
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+    </row>
+    <row r="33" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I33" s="23">
+        <f>SUM(I6:I32)</f>
+        <v>79709</v>
+      </c>
+      <c r="J33" s="38" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="2">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="2">
         <v>46203</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C46" t="s">
         <v>167</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>197</v>
       </c>
     </row>
@@ -5398,7 +5464,7 @@
     <mergeCell ref="C2:G3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="خطأ" error="يرجى اختيار موظف من القائمة" sqref="B6:B22" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="خطأ" error="يرجى اختيار موظف من القائمة" sqref="B6:B23" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>INDIRECT("الموظفين!$B$4:$B$23")</formula1>
     </dataValidation>
   </dataValidations>
@@ -5423,12 +5489,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
     </row>
     <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -5909,16 +5975,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -6302,15 +6368,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">

--- a/Cafe 2M.xlsx
+++ b/Cafe 2M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GHOST\OneDrive\سطح المكتب\cafe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB4191C-B042-41FA-8C93-CA6751DFC753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7040915D-86D7-435C-8011-776D657F5636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الموظفين" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="198">
   <si>
     <t>المشتريات اليومية</t>
   </si>
@@ -405,9 +405,6 @@
   </si>
   <si>
     <t>تشوكلت كيك</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دون فاتورة حتي الان </t>
   </si>
   <si>
     <t>الاجمالي</t>
@@ -651,12 +648,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="178"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -952,42 +957,42 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -996,10 +1001,10 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1008,119 +1013,125 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1620,24 +1631,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="50" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1645,13 +1656,13 @@
       <c r="A5" s="14">
         <v>1</v>
       </c>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="53" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="54">
+      <c r="C5" s="52" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="53">
         <v>1099724995</v>
       </c>
     </row>
@@ -1659,13 +1670,13 @@
       <c r="A6" s="14">
         <v>2</v>
       </c>
-      <c r="B6" s="52" t="s">
+      <c r="B6" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="54">
         <v>1098610851</v>
       </c>
     </row>
@@ -1673,13 +1684,13 @@
       <c r="A7" s="14">
         <v>3</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="55">
+      <c r="C7" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="54">
         <v>1022948840</v>
       </c>
     </row>
@@ -1687,13 +1698,13 @@
       <c r="A8" s="14">
         <v>4</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B8" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="55">
+      <c r="C8" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="54">
         <v>1094787318</v>
       </c>
     </row>
@@ -1701,13 +1712,13 @@
       <c r="A9" s="14">
         <v>5</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="D9" s="55">
+      <c r="C9" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="54">
         <v>1141286890</v>
       </c>
     </row>
@@ -1715,13 +1726,13 @@
       <c r="A10" s="14">
         <v>6</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="53" t="s">
-        <v>177</v>
-      </c>
-      <c r="D10" s="55">
+      <c r="C10" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="54">
         <v>1203252448</v>
       </c>
     </row>
@@ -1729,13 +1740,13 @@
       <c r="A11" s="14">
         <v>7</v>
       </c>
-      <c r="B11" s="52" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" s="55">
+      <c r="B11" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="54">
         <v>1273884672</v>
       </c>
     </row>
@@ -1743,13 +1754,13 @@
       <c r="A12" s="14">
         <v>8</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="D12" s="55">
+      <c r="C12" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="54">
         <v>1556027058</v>
       </c>
     </row>
@@ -1757,13 +1768,13 @@
       <c r="A13" s="14">
         <v>9</v>
       </c>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="55">
+      <c r="D13" s="54">
         <v>1148115761</v>
       </c>
     </row>
@@ -1771,13 +1782,13 @@
       <c r="A14" s="14">
         <v>10</v>
       </c>
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="D14" s="55">
+      <c r="C14" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="54">
         <v>1228413897</v>
       </c>
     </row>
@@ -1785,13 +1796,13 @@
       <c r="A15" s="14">
         <v>11</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="D15" s="55">
+      <c r="C15" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="D15" s="54">
         <v>1288766508</v>
       </c>
     </row>
@@ -1799,13 +1810,13 @@
       <c r="A16" s="14">
         <v>12</v>
       </c>
-      <c r="B16" s="52" t="s">
+      <c r="B16" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="D16" s="55">
+      <c r="C16" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="54">
         <v>1206196377</v>
       </c>
     </row>
@@ -1813,13 +1824,13 @@
       <c r="A17" s="14">
         <v>13</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="52" t="s">
         <v>97</v>
       </c>
-      <c r="D17" s="55">
+      <c r="D17" s="54">
         <v>1033075725</v>
       </c>
     </row>
@@ -1827,13 +1838,13 @@
       <c r="A18" s="14">
         <v>14</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="54">
         <v>1097710346</v>
       </c>
     </row>
@@ -1841,13 +1852,13 @@
       <c r="A19" s="14">
         <v>15</v>
       </c>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="53" t="s">
-        <v>178</v>
-      </c>
-      <c r="D19" s="55">
+      <c r="C19" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="54">
         <v>1221210579</v>
       </c>
     </row>
@@ -1855,37 +1866,37 @@
       <c r="A20" s="14">
         <v>16</v>
       </c>
-      <c r="B20" s="52" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>177</v>
-      </c>
-      <c r="D20" s="56"/>
+      <c r="B20" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="D20" s="55"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>17</v>
       </c>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="D21" s="56"/>
+      <c r="C21" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" s="55"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>18</v>
       </c>
-      <c r="B22" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="C22" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="D22" s="54">
+      <c r="B22" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="53">
         <v>1028966193</v>
       </c>
     </row>
@@ -1893,35 +1904,35 @@
       <c r="A23" s="14">
         <v>19</v>
       </c>
-      <c r="B23" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="C23" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="D23" s="56"/>
+      <c r="B23" s="56" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="D23" s="55"/>
     </row>
     <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>20</v>
       </c>
-      <c r="B24" s="58" t="s">
-        <v>181</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>176</v>
-      </c>
-      <c r="D24" s="56"/>
+      <c r="B24" s="57" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="55"/>
     </row>
     <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>21</v>
       </c>
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="52" t="s">
         <v>182</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>183</v>
       </c>
       <c r="D25" s="40">
         <v>1277585870</v>
@@ -1932,10 +1943,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="C26" s="53" t="s">
-        <v>176</v>
+        <v>140</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>175</v>
       </c>
       <c r="D26" s="40">
         <v>1020633821</v>
@@ -1946,7 +1957,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -1956,7 +1967,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -1966,7 +1977,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -2020,16 +2031,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
@@ -2295,37 +2306,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B3" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="D3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="E3" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="F3" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="G3" s="27" t="s">
         <v>128</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2339,7 +2350,7 @@
         <v>69</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E4" s="46" t="s">
         <v>73</v>
@@ -2360,7 +2371,7 @@
         <v>246428</v>
       </c>
       <c r="C5" s="43">
-        <f>SUM('المشتريات اليومية'!G37)</f>
+        <f>SUM('المشتريات اليومية'!G36)</f>
         <v>163610</v>
       </c>
       <c r="D5" s="43">
@@ -2368,11 +2379,11 @@
       </c>
       <c r="E5" s="43">
         <f>SUM(الرواتب!I6:I32)</f>
-        <v>79709</v>
+        <v>86914</v>
       </c>
       <c r="F5" s="43">
         <f>SUM(E21)</f>
-        <v>-25976</v>
+        <v>-33181</v>
       </c>
       <c r="G5" s="44"/>
     </row>
@@ -2393,13 +2404,13 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E16" s="1">
         <f>SUM(C5:E5)</f>
-        <v>272404</v>
+        <v>279609</v>
       </c>
     </row>
     <row r="21" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E21" s="1">
         <f>SUM(B5-E16)</f>
-        <v>-25976</v>
+        <v>-33181</v>
       </c>
     </row>
   </sheetData>
@@ -2431,15 +2442,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -2928,7 +2939,7 @@
   <sheetPr>
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2942,16 +2953,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -2983,7 +2994,7 @@
       <c r="L3" s="29"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="48">
+      <c r="A4" s="47">
         <v>46180</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -3002,7 +3013,7 @@
       <c r="L4" s="29"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="48">
+      <c r="A5" s="47">
         <v>46181</v>
       </c>
       <c r="B5" s="39" t="s">
@@ -3021,7 +3032,7 @@
       <c r="L5" s="29"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="48">
+      <c r="A6" s="47">
         <v>46182</v>
       </c>
       <c r="B6" s="39" t="s">
@@ -3040,11 +3051,11 @@
       <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="48">
+      <c r="A7" s="47">
         <v>46183</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -3059,11 +3070,11 @@
       <c r="L7" s="3"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="48">
+      <c r="A8" s="47">
         <v>46184</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -3078,7 +3089,7 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="48">
+      <c r="A9" s="47">
         <v>46185</v>
       </c>
       <c r="B9" s="39" t="s">
@@ -3097,7 +3108,7 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="48">
+      <c r="A10" s="47">
         <v>46186</v>
       </c>
       <c r="B10" s="39" t="s">
@@ -3116,7 +3127,7 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="48">
+      <c r="A11" s="47">
         <v>46187</v>
       </c>
       <c r="B11" s="39" t="s">
@@ -3135,11 +3146,11 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="48">
+      <c r="A12" s="47">
         <v>46188</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -3151,7 +3162,7 @@
       <c r="H12" s="14"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="48">
+      <c r="A13" s="47">
         <v>46189</v>
       </c>
       <c r="B13" s="39" t="s">
@@ -3169,11 +3180,11 @@
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="48">
+      <c r="A14" s="47">
         <v>46190</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -3186,11 +3197,11 @@
       <c r="H14" s="14"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="48">
+      <c r="A15" s="47">
         <v>46191</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -3203,7 +3214,7 @@
       <c r="H15" s="14"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="48">
+      <c r="A16" s="47">
         <v>46190</v>
       </c>
       <c r="B16" s="39" t="s">
@@ -3219,7 +3230,7 @@
       <c r="H16" s="14"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="48">
+      <c r="A17" s="47">
         <v>46193</v>
       </c>
       <c r="B17" s="39" t="s">
@@ -3236,7 +3247,7 @@
       <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="48">
+      <c r="A18" s="47">
         <v>46194</v>
       </c>
       <c r="B18" s="39" t="s">
@@ -3253,7 +3264,7 @@
       <c r="H18" s="14"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="48">
+      <c r="A19" s="47">
         <v>46195</v>
       </c>
       <c r="B19" s="39" t="s">
@@ -3270,7 +3281,7 @@
       <c r="H19" s="14"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="48">
+      <c r="A20" s="47">
         <v>46196</v>
       </c>
       <c r="B20" s="39" t="s">
@@ -3287,11 +3298,11 @@
       <c r="H20" s="14"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="48">
+      <c r="A21" s="47">
         <v>46197</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
@@ -3304,11 +3315,11 @@
       <c r="H21" s="14"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="48">
+      <c r="A22" s="47">
         <v>46198</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
@@ -3320,61 +3331,71 @@
       <c r="H22" s="14"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="48"/>
-      <c r="B23" s="39"/>
+      <c r="A23" s="47">
+        <v>46199</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>22</v>
+      </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="14"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="14"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="48">
-        <v>46199</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="33">
+      <c r="G23" s="33">
         <f>3920+3150</f>
         <v>7070</v>
       </c>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="47">
+        <v>46200</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="25">
+        <v>1635</v>
+      </c>
       <c r="H24" s="14"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="48">
-        <v>46200</v>
+      <c r="A25" s="47">
+        <v>46201</v>
       </c>
       <c r="B25" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>139</v>
+        <v>187</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
       <c r="G25" s="25">
-        <v>1635</v>
+        <v>13425</v>
       </c>
       <c r="H25" s="14"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="48">
+      <c r="A26" s="47">
         <v>46201</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D26" s="30" t="s">
         <v>102</v>
@@ -3382,20 +3403,20 @@
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
       <c r="G26" s="25">
-        <v>13425</v>
+        <v>5895</v>
       </c>
       <c r="H26" s="14"/>
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="48">
+      <c r="A27" s="47">
         <v>46201</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D27" s="30" t="s">
         <v>102</v>
@@ -3403,19 +3424,19 @@
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="25">
-        <v>5895</v>
+        <v>225</v>
       </c>
       <c r="H27" s="14"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="48">
+      <c r="A28" s="47">
         <v>46201</v>
       </c>
       <c r="B28" s="30" t="s">
         <v>111</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D28" s="30" t="s">
         <v>102</v>
@@ -3423,189 +3444,177 @@
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
       <c r="G28" s="25">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="H28" s="14"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="48">
+      <c r="A29" s="47">
         <v>46201</v>
       </c>
       <c r="B29" s="30" t="s">
         <v>111</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
       <c r="G29" s="25">
-        <v>50</v>
+        <v>925</v>
       </c>
       <c r="H29" s="14"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="48">
-        <v>46201</v>
+      <c r="A30" s="47">
+        <v>46202</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
       <c r="G30" s="25">
-        <v>925</v>
+        <v>450</v>
       </c>
       <c r="H30" s="14"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="48">
+      <c r="A31" s="47">
         <v>46202</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>18</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>118</v>
+        <v>187</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
       <c r="G31" s="25">
-        <v>450</v>
+        <v>8440</v>
       </c>
       <c r="H31" s="14"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="48">
+      <c r="A32" s="47">
         <v>46202</v>
       </c>
       <c r="B32" s="30" t="s">
         <v>18</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
       <c r="G32" s="25">
-        <v>8440</v>
+        <v>1046</v>
       </c>
       <c r="H32" s="14"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="48">
+      <c r="A33" s="47">
         <v>46202</v>
       </c>
       <c r="B33" s="30" t="s">
         <v>18</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
       <c r="G33" s="25">
-        <v>1046</v>
-      </c>
-      <c r="H33" s="14"/>
+        <v>8000</v>
+      </c>
+      <c r="H33" s="28"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="48">
-        <v>46202</v>
+      <c r="A34" s="47">
+        <v>46203</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="E34" s="17"/>
       <c r="F34" s="17"/>
       <c r="G34" s="25">
-        <v>8000</v>
-      </c>
-      <c r="H34" s="28" t="s">
-        <v>119</v>
-      </c>
+        <v>1700</v>
+      </c>
+      <c r="H34" s="14"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="48">
+      <c r="A35" s="47">
         <v>46203</v>
       </c>
       <c r="B35" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
       <c r="G35" s="25">
-        <v>1700</v>
+        <v>350</v>
       </c>
       <c r="H35" s="14"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="48">
-        <v>46203</v>
-      </c>
-      <c r="B36" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="D36" s="30" t="s">
+    <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A36" s="58"/>
+      <c r="B36" s="29"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="59">
+        <f>SUM(G4:G35)</f>
+        <v>163610</v>
+      </c>
+      <c r="H36" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="25">
-        <v>350</v>
-      </c>
-      <c r="H36" s="14"/>
     </row>
     <row r="37" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="59"/>
-      <c r="B37" s="29"/>
+      <c r="A37" s="58"/>
+      <c r="B37" s="29" t="str">
+        <f t="shared" ref="B37:B39" si="0">IF(A37="","",TEXT(A37,"dddd"))</f>
+        <v/>
+      </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="60">
-        <f>SUM(G4:G36)</f>
-        <v>163610</v>
-      </c>
-      <c r="H37" s="38" t="s">
-        <v>190</v>
-      </c>
+      <c r="G37" s="1"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="59"/>
-      <c r="B38" s="29" t="str">
-        <f t="shared" ref="B38:B40" si="0">IF(A38="","",TEXT(A38,"dddd"))</f>
+      <c r="A38" s="58"/>
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="E38" s="1"/>
@@ -3613,7 +3622,7 @@
       <c r="G38" s="1"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="59"/>
+      <c r="A39" s="2"/>
       <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3621,22 +3630,12 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3658,12 +3657,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="66" t="s">
-        <v>159</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="A1" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
     </row>
     <row r="3" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -3680,50 +3679,50 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48">
+      <c r="A4" s="47">
         <v>46218</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C4" s="30">
         <v>890</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48">
+      <c r="A5" s="47">
         <v>46195</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C5" s="30">
         <v>890</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="48">
+      <c r="A6" s="47">
         <v>46200</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C6" s="30">
         <f>690+200</f>
         <v>890</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="48">
+      <c r="A7" s="47">
         <v>46200</v>
       </c>
       <c r="B7" s="30" t="s">
@@ -3735,7 +3734,7 @@
       <c r="D7" s="37"/>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="48">
+      <c r="A8" s="47">
         <v>46201</v>
       </c>
       <c r="B8" s="30" t="s">
@@ -3747,7 +3746,7 @@
       <c r="D8" s="37"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="48">
+      <c r="A9" s="47">
         <v>46201</v>
       </c>
       <c r="B9" s="30" t="s">
@@ -3759,7 +3758,7 @@
       <c r="D9" s="37"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="48">
+      <c r="A10" s="47">
         <v>46201</v>
       </c>
       <c r="B10" s="30" t="s">
@@ -3771,7 +3770,7 @@
       <c r="D10" s="37"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="48">
+      <c r="A11" s="47">
         <v>46201</v>
       </c>
       <c r="B11" s="30" t="s">
@@ -3783,7 +3782,7 @@
       <c r="D11" s="37"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="48">
+      <c r="A12" s="47">
         <v>46201</v>
       </c>
       <c r="B12" s="30" t="s">
@@ -3795,7 +3794,7 @@
       <c r="D12" s="37"/>
     </row>
     <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="48">
+      <c r="A13" s="47">
         <v>46202</v>
       </c>
       <c r="B13" s="30" t="s">
@@ -3807,7 +3806,7 @@
       <c r="D13" s="37"/>
     </row>
     <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="48">
+      <c r="A14" s="47">
         <v>46202</v>
       </c>
       <c r="B14" s="30" t="s">
@@ -3819,7 +3818,7 @@
       <c r="D14" s="37"/>
     </row>
     <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="48">
+      <c r="A15" s="47">
         <v>46202</v>
       </c>
       <c r="B15" s="30" t="s">
@@ -3831,7 +3830,7 @@
       <c r="D15" s="37"/>
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="48">
+      <c r="A16" s="47">
         <v>46202</v>
       </c>
       <c r="B16" s="30" t="s">
@@ -3844,7 +3843,7 @@
     </row>
     <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="30">
         <v>18000</v>
@@ -3853,7 +3852,7 @@
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="30">
         <v>1500</v>
@@ -3862,7 +3861,7 @@
     </row>
     <row r="19" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C19" s="30">
         <v>2000</v>
@@ -3875,7 +3874,7 @@
         <v>29085</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3981,24 +3980,25 @@
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="5" width="12" customWidth="1"/>
-    <col min="6" max="9" width="16" customWidth="1"/>
+    <col min="6" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
@@ -4024,14 +4024,14 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="67" t="s">
-        <v>192</v>
-      </c>
-      <c r="G7" s="67"/>
+      <c r="F7" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="G7" s="66"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
     </row>
     <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
@@ -4062,7 +4062,7 @@
         <v>92</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>9</v>
@@ -4216,8 +4216,8 @@
       <c r="I19" s="41">
         <v>2685</v>
       </c>
-      <c r="J19" s="50" t="s">
-        <v>171</v>
+      <c r="J19" s="49" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -4236,8 +4236,8 @@
       <c r="I20" s="41">
         <v>2193</v>
       </c>
-      <c r="J20" s="50" t="s">
-        <v>171</v>
+      <c r="J20" s="49" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -4256,7 +4256,7 @@
       <c r="I21" s="41">
         <v>6445</v>
       </c>
-      <c r="J21" s="49"/>
+      <c r="J21" s="48"/>
       <c r="N21" s="3"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -4275,7 +4275,7 @@
       <c r="I22" s="41">
         <v>8050</v>
       </c>
-      <c r="J22" s="49"/>
+      <c r="J22" s="48"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
@@ -4293,7 +4293,7 @@
       <c r="I23" s="41">
         <v>11755</v>
       </c>
-      <c r="J23" s="49"/>
+      <c r="J23" s="48"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
@@ -4311,7 +4311,7 @@
       <c r="I24" s="41">
         <v>6955</v>
       </c>
-      <c r="J24" s="49"/>
+      <c r="J24" s="48"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
@@ -4329,8 +4329,8 @@
       <c r="I25" s="41">
         <v>10900</v>
       </c>
-      <c r="J25" s="50" t="s">
-        <v>169</v>
+      <c r="J25" s="49" t="s">
+        <v>168</v>
       </c>
       <c r="L25" s="1"/>
     </row>
@@ -4350,7 +4350,7 @@
       <c r="I26" s="41">
         <v>7150</v>
       </c>
-      <c r="J26" s="49"/>
+      <c r="J26" s="48"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
@@ -4368,7 +4368,7 @@
       <c r="I27" s="41">
         <v>10020</v>
       </c>
-      <c r="J27" s="49"/>
+      <c r="J27" s="48"/>
       <c r="L27" s="1"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -4387,7 +4387,7 @@
       <c r="I28" s="41">
         <v>8550</v>
       </c>
-      <c r="J28" s="49"/>
+      <c r="J28" s="48"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
@@ -4405,7 +4405,7 @@
       <c r="I29" s="41">
         <v>5155</v>
       </c>
-      <c r="J29" s="49"/>
+      <c r="J29" s="48"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
@@ -4423,7 +4423,7 @@
       <c r="I30" s="41">
         <v>9100</v>
       </c>
-      <c r="J30" s="49"/>
+      <c r="J30" s="48"/>
       <c r="N30" s="3"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -4442,7 +4442,7 @@
       <c r="I31" s="41">
         <v>11850</v>
       </c>
-      <c r="J31" s="49"/>
+      <c r="J31" s="48"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
@@ -4460,8 +4460,8 @@
       <c r="I32" s="41">
         <v>10700</v>
       </c>
-      <c r="J32" s="50" t="s">
-        <v>170</v>
+      <c r="J32" s="49" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -4480,7 +4480,7 @@
       <c r="I33" s="41">
         <v>9700</v>
       </c>
-      <c r="J33" s="49"/>
+      <c r="J33" s="48"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
@@ -4498,7 +4498,7 @@
       <c r="I34" s="41">
         <v>11000</v>
       </c>
-      <c r="J34" s="49"/>
+      <c r="J34" s="48"/>
     </row>
     <row r="35" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
@@ -4516,7 +4516,7 @@
       <c r="I35" s="41">
         <v>15032</v>
       </c>
-      <c r="J35" s="49"/>
+      <c r="J35" s="48"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
@@ -4534,8 +4534,8 @@
       <c r="I36" s="41">
         <v>19573</v>
       </c>
-      <c r="J36" s="50" t="s">
-        <v>172</v>
+      <c r="J36" s="49" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -4545,13 +4545,13 @@
       <c r="B37" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="50">
+      <c r="C37" s="49">
         <v>9665</v>
       </c>
-      <c r="D37" s="50">
+      <c r="D37" s="49">
         <v>600</v>
       </c>
-      <c r="E37" s="50">
+      <c r="E37" s="49">
         <v>325</v>
       </c>
       <c r="F37" s="26">
@@ -4568,7 +4568,7 @@
         <v>13390</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -4578,7 +4578,7 @@
       <c r="B38" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="50">
+      <c r="C38" s="49">
         <f>4640+8560</f>
         <v>13200</v>
       </c>
@@ -4677,12 +4677,12 @@
       <c r="J40" s="14"/>
     </row>
     <row r="41" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I41" s="47">
+      <c r="I41" s="71">
         <f>SUM(I17:I40)</f>
         <v>246428</v>
       </c>
       <c r="J41" s="38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="9:9" x14ac:dyDescent="0.25">
@@ -4702,7 +4702,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="F7:G8"/>
   </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup scale="56" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4737,31 +4737,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64"/>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
+      <c r="A1" s="65"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C2" s="70" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
+      <c r="C2" s="69" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
     </row>
     <row r="5" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -4789,7 +4789,7 @@
         <v>36</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J5" s="15" t="s">
         <v>95</v>
@@ -4797,17 +4797,17 @@
       <c r="K5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="V5" s="69"/>
+      <c r="U5" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>1</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="30"/>
       <c r="D6" s="25"/>
@@ -4817,14 +4817,14 @@
         <v>270</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H6" s="26"/>
-      <c r="I6" s="30"/>
+      <c r="I6" s="72"/>
       <c r="J6" s="30"/>
       <c r="K6" s="30"/>
       <c r="U6" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="V6" s="30" t="s">
         <v>94</v>
@@ -4848,10 +4848,10 @@
       </c>
       <c r="J7" s="30"/>
       <c r="K7" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="U7" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V7" s="30">
         <v>1665</v>
@@ -4875,10 +4875,10 @@
       </c>
       <c r="J8" s="30"/>
       <c r="K8" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="U8" s="30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="V8" s="30">
         <v>300</v>
@@ -4902,10 +4902,10 @@
       </c>
       <c r="J9" s="30"/>
       <c r="K9" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="U9" s="30" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="V9" s="30">
         <v>4104</v>
@@ -4929,10 +4929,10 @@
       </c>
       <c r="J10" s="30"/>
       <c r="K10" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U10" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="V10" s="30">
         <v>2000</v>
@@ -4951,15 +4951,15 @@
       <c r="F11" s="41"/>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
-      <c r="I11" s="72">
+      <c r="I11" s="73">
         <v>2750</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="U11" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="V11" s="30">
         <v>9000</v>
@@ -4970,7 +4970,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C12" s="30"/>
       <c r="D12" s="25"/>
@@ -4981,17 +4981,17 @@
       </c>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
-      <c r="I12" s="72">
+      <c r="I12" s="73">
         <v>3000</v>
       </c>
       <c r="J12" s="30">
         <v>-520</v>
       </c>
       <c r="K12" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="U12" s="30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="V12" s="30">
         <v>1290</v>
@@ -5015,10 +5015,10 @@
       </c>
       <c r="J13" s="30"/>
       <c r="K13" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="U13" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="V13" s="30">
         <v>1500</v>
@@ -5029,7 +5029,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="25"/>
@@ -5040,10 +5040,13 @@
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
+      <c r="I14" s="70">
+        <v>3000</v>
+      </c>
       <c r="J14" s="30"/>
       <c r="K14" s="30"/>
       <c r="U14" s="30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="V14" s="30">
         <v>6120</v>
@@ -5067,10 +5070,10 @@
       </c>
       <c r="J15" s="30"/>
       <c r="K15" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U15" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="V15" s="30">
         <v>8350</v>
@@ -5094,10 +5097,10 @@
       </c>
       <c r="J16" s="30"/>
       <c r="K16" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U16" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V16" s="30">
         <v>4000</v>
@@ -5118,12 +5121,12 @@
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="26"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30">
+      <c r="I17" s="30">
         <v>1770</v>
       </c>
+      <c r="J17" s="30"/>
       <c r="K17" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -5141,12 +5144,12 @@
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
-      <c r="I18" s="71">
+      <c r="I18" s="74">
         <v>600</v>
       </c>
       <c r="J18" s="30"/>
       <c r="K18" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -5162,12 +5165,12 @@
       <c r="F19" s="41"/>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
-      <c r="I19" s="72">
+      <c r="I19" s="73">
         <v>1000</v>
       </c>
       <c r="J19" s="30"/>
       <c r="K19" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -5184,8 +5187,8 @@
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
       <c r="I20" s="30">
-        <f>6000+1500</f>
-        <v>7500</v>
+        <f>6000+1000+1500+500</f>
+        <v>9000</v>
       </c>
       <c r="J20" s="30"/>
       <c r="K20" s="30"/>
@@ -5193,7 +5196,7 @@
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C21" s="30"/>
       <c r="D21" s="25"/>
@@ -5202,7 +5205,8 @@
       <c r="G21" s="26"/>
       <c r="H21" s="26"/>
       <c r="I21" s="30">
-        <v>2750</v>
+        <f>2750+1660</f>
+        <v>4410</v>
       </c>
       <c r="J21" s="30"/>
       <c r="K21" s="30"/>
@@ -5222,7 +5226,7 @@
       </c>
       <c r="G22" s="26"/>
       <c r="H22" s="26"/>
-      <c r="I22" s="30"/>
+      <c r="I22" s="72"/>
       <c r="J22" s="30"/>
       <c r="K22" s="30"/>
     </row>
@@ -5246,7 +5250,7 @@
       </c>
       <c r="J23" s="30"/>
       <c r="K23" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -5254,7 +5258,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="28"/>
@@ -5265,7 +5269,7 @@
       </c>
       <c r="G24" s="30"/>
       <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
+      <c r="I24" s="72"/>
       <c r="J24" s="30"/>
       <c r="K24" s="30"/>
     </row>
@@ -5274,7 +5278,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="28"/>
@@ -5287,7 +5291,7 @@
       </c>
       <c r="J25" s="30"/>
       <c r="K25" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -5295,7 +5299,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C26" s="30"/>
       <c r="D26" s="28"/>
@@ -5308,7 +5312,7 @@
       </c>
       <c r="J26" s="30"/>
       <c r="K26" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -5316,7 +5320,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C27" s="30"/>
       <c r="D27" s="28"/>
@@ -5329,7 +5333,7 @@
       </c>
       <c r="J27" s="30"/>
       <c r="K27" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -5337,7 +5341,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C28" s="30"/>
       <c r="D28" s="28"/>
@@ -5350,7 +5354,7 @@
       </c>
       <c r="J28" s="30"/>
       <c r="K28" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -5358,7 +5362,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C29" s="30"/>
       <c r="D29" s="28"/>
@@ -5371,7 +5375,7 @@
       </c>
       <c r="J29" s="30"/>
       <c r="K29" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -5379,7 +5383,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C30" s="30"/>
       <c r="D30" s="28"/>
@@ -5390,11 +5394,11 @@
       <c r="G30" s="30"/>
       <c r="H30" s="30"/>
       <c r="I30" s="30">
-        <v>3725</v>
+        <v>3000</v>
       </c>
       <c r="J30" s="30"/>
       <c r="K30" s="30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5402,7 +5406,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C31" s="30"/>
       <c r="D31" s="28"/>
@@ -5415,15 +5419,15 @@
       </c>
       <c r="J31" s="30"/>
       <c r="K31" s="30" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>26</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -5437,24 +5441,25 @@
       <c r="J32" s="30"/>
       <c r="K32" s="30"/>
     </row>
-    <row r="33" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I33" s="23">
         <f>SUM(I6:I32)</f>
-        <v>79709</v>
+        <v>86914</v>
       </c>
       <c r="J33" s="38" t="s">
-        <v>191</v>
-      </c>
-    </row>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="2">
         <v>46203</v>
       </c>
       <c r="C46" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -5489,12 +5494,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
     </row>
     <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -5511,10 +5516,10 @@
       </c>
       <c r="H3" s="26">
         <f>SUM(C4:C462)</f>
-        <v>6150</v>
+        <v>2085</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5578,16 +5583,16 @@
       <c r="D8" s="39"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="61" t="s">
-        <v>194</v>
-      </c>
-      <c r="C9" s="63">
+      <c r="B9" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="62">
         <v>20</v>
       </c>
-      <c r="D9" s="62"/>
+      <c r="D9" s="61"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
@@ -5626,16 +5631,16 @@
       <c r="D12" s="39"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="61" t="s">
-        <v>194</v>
-      </c>
-      <c r="C13" s="63">
+      <c r="B13" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="C13" s="62">
         <v>45</v>
       </c>
-      <c r="D13" s="62"/>
+      <c r="D13" s="61"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
@@ -5733,7 +5738,7 @@
         <v>100</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5747,19 +5752,15 @@
         <v>100</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>46203</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="25">
-        <v>4065</v>
-      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="39"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5811,11 +5812,11 @@
       <c r="D27" s="39"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="48">
+      <c r="A28" s="47">
         <v>46203</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C28" s="30">
         <v>115</v>
@@ -5857,7 +5858,7 @@
         <v>100</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5975,16 +5976,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -6368,15 +6369,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">

--- a/Cafe 2M.xlsx
+++ b/Cafe 2M.xlsx
@@ -8,27 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GHOST\OneDrive\سطح المكتب\cafe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7040915D-86D7-435C-8011-776D657F5636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF5C4E2-A920-46DE-A058-21F1FC740022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الموظفين" sheetId="2" r:id="rId1"/>
     <sheet name="الإيرادات اليومية" sheetId="3" r:id="rId2"/>
-    <sheet name="المشتريات اليومية" sheetId="4" r:id="rId3"/>
-    <sheet name="المصروفات" sheetId="5" r:id="rId4"/>
-    <sheet name="تقفيلة اليوم" sheetId="6" r:id="rId5"/>
-    <sheet name="الرواتب" sheetId="7" r:id="rId6"/>
-    <sheet name="سلف الموظفين" sheetId="8" r:id="rId7"/>
+    <sheet name="تقفيلة اليوم" sheetId="6" r:id="rId3"/>
+    <sheet name="المشتريات اليومية" sheetId="4" r:id="rId4"/>
+    <sheet name="المصروفات" sheetId="5" r:id="rId5"/>
+    <sheet name="سلف الموظفين" sheetId="8" r:id="rId6"/>
+    <sheet name="ملخص شهري" sheetId="13" r:id="rId7"/>
     <sheet name="المخزون" sheetId="10" r:id="rId8"/>
     <sheet name="الجرد" sheetId="11" r:id="rId9"/>
     <sheet name="الموردين" sheetId="12" r:id="rId10"/>
-    <sheet name="ملخص شهري" sheetId="13" r:id="rId11"/>
+    <sheet name="الرواتب" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">الرواتب!$A$1:$K$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">المصروفات!$A$1:$D$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'تقفيلة اليوم'!$A$6:$J$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">الرواتب!$A$1:$K$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">المصروفات!$A$1:$D$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'تقفيلة اليوم'!$A$6:$J$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'ملخص شهري'!$A$1:$H$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="199">
   <si>
     <t>المشتريات اليومية</t>
   </si>
@@ -263,9 +264,6 @@
     <t>مدفوع</t>
   </si>
   <si>
-    <t>الملخص الشهري</t>
-  </si>
-  <si>
     <t>إجمالي الإيرادات</t>
   </si>
   <si>
@@ -512,9 +510,6 @@
     <t>محمود محمد صبحي</t>
   </si>
   <si>
-    <t>عبد الله الغزولي</t>
-  </si>
-  <si>
     <t>محمد اسامة</t>
   </si>
   <si>
@@ -641,14 +636,23 @@
     <t>كانت في المصاريف النثرية</t>
   </si>
   <si>
-    <t>لحد 30/6</t>
+    <t>ذ</t>
+  </si>
+  <si>
+    <t>م جمعة</t>
+  </si>
+  <si>
+    <t>عبد الله الغزالي</t>
+  </si>
+  <si>
+    <t>الفتره من 6/7 الي  : 6/30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -838,8 +842,16 @@
       <charset val="178"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -877,6 +889,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -955,12 +978,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1100,11 +1124,36 @@
     <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1119,24 +1168,12 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="26" fillId="6" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="3" builtinId="26"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1266,6 +1303,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A6F27E3D-FBAF-4743-A0A3-D8E2D9B03B04}" name="Table2" displayName="Table2" ref="A4:G6" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A4:G6" xr:uid="{A6F27E3D-FBAF-4743-A0A3-D8E2D9B03B04}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{A998BA95-B09C-44A1-A227-B8F1FF4998BD}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{7F618648-8E50-4DC0-B288-6CD993840FB4}" name="Column2" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{EF3645F5-0BE4-48DB-B29E-C177BB47CC4C}" name="Column3" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{EB69A2FB-DBB9-4FE5-BED5-8121EF9313B1}" name="Column4" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{FD215D26-D2BF-41DB-B058-CF22763E6EE0}" name="Column5" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{7245048F-85FE-4E7F-B3F5-156C2BE4C803}" name="Column6" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{9565D7A7-9C50-40C6-ADD4-AC220B8E1416}" name="Column7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1503CE6A-6F5B-42CF-B835-8677243A5452}" name="Table1" displayName="Table1" ref="A3:H25" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A3:H25" xr:uid="{1503CE6A-6F5B-42CF-B835-8677243A5452}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:H25">
@@ -1282,22 +1335,6 @@
     <tableColumn id="8" xr3:uid="{EF20BE48-0E95-4340-A877-1CC6DA1E89B4}" name="المتبقي"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A6F27E3D-FBAF-4743-A0A3-D8E2D9B03B04}" name="Table2" displayName="Table2" ref="A3:G5" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="A3:G5" xr:uid="{A6F27E3D-FBAF-4743-A0A3-D8E2D9B03B04}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A998BA95-B09C-44A1-A227-B8F1FF4998BD}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{7F618648-8E50-4DC0-B288-6CD993840FB4}" name="Column2" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{EF3645F5-0BE4-48DB-B29E-C177BB47CC4C}" name="Column3" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{EB69A2FB-DBB9-4FE5-BED5-8121EF9313B1}" name="Column4" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{FD215D26-D2BF-41DB-B058-CF22763E6EE0}" name="Column5" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{7245048F-85FE-4E7F-B3F5-156C2BE4C803}" name="Column6" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{9565D7A7-9C50-40C6-ADD4-AC220B8E1416}" name="Column7"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1631,12 +1668,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
@@ -1657,10 +1694,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D5" s="53">
         <v>1099724995</v>
@@ -1671,10 +1708,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6" s="54">
         <v>1098610851</v>
@@ -1685,10 +1722,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D7" s="54">
         <v>1022948840</v>
@@ -1699,10 +1736,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D8" s="54">
         <v>1094787318</v>
@@ -1713,10 +1750,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D9" s="54">
         <v>1141286890</v>
@@ -1727,10 +1764,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D10" s="54">
         <v>1203252448</v>
@@ -1741,10 +1778,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D11" s="54">
         <v>1273884672</v>
@@ -1755,10 +1792,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D12" s="54">
         <v>1556027058</v>
@@ -1769,10 +1806,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" s="54">
         <v>1148115761</v>
@@ -1783,10 +1820,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D14" s="54">
         <v>1228413897</v>
@@ -1797,10 +1834,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D15" s="54">
         <v>1288766508</v>
@@ -1811,10 +1848,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D16" s="54">
         <v>1206196377</v>
@@ -1825,10 +1862,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" s="54">
         <v>1033075725</v>
@@ -1839,10 +1876,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D18" s="54">
         <v>1097710346</v>
@@ -1853,10 +1890,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D19" s="54">
         <v>1221210579</v>
@@ -1867,10 +1904,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D20" s="55"/>
     </row>
@@ -1879,10 +1916,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D21" s="55"/>
     </row>
@@ -1891,10 +1928,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D22" s="53">
         <v>1028966193</v>
@@ -1905,10 +1942,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D23" s="55"/>
     </row>
@@ -1917,10 +1954,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="57" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D24" s="55"/>
     </row>
@@ -1929,10 +1966,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="57" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D25" s="40">
         <v>1277585870</v>
@@ -1943,10 +1980,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D26" s="40">
         <v>1020633821</v>
@@ -1957,7 +1994,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -1967,7 +2004,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -1977,7 +2014,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -2031,16 +2068,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
@@ -2290,2431 +2327,12 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF50A280"/>
-  </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="46" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="45">
-        <v>6</v>
-      </c>
-      <c r="B5" s="43">
-        <f>SUM('تقفيلة اليوم'!I17:I40)</f>
-        <v>246428</v>
-      </c>
-      <c r="C5" s="43">
-        <f>SUM('المشتريات اليومية'!G36)</f>
-        <v>163610</v>
-      </c>
-      <c r="D5" s="43">
-        <v>29085</v>
-      </c>
-      <c r="E5" s="43">
-        <f>SUM(الرواتب!I6:I32)</f>
-        <v>86914</v>
-      </c>
-      <c r="F5" s="43">
-        <f>SUM(E21)</f>
-        <v>-33181</v>
-      </c>
-      <c r="G5" s="44"/>
-    </row>
-    <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E16" s="1">
-        <f>SUM(C5:E5)</f>
-        <v>279609</v>
-      </c>
-    </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="1">
-        <f>SUM(B5-E16)</f>
-        <v>-33181</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFFC000"/>
-  </sheetPr>
-  <dimension ref="A1:K35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="21">
-        <v>46174</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="14"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="21">
-        <v>46175</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="21">
-        <v>46176</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
-        <v>46177</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
-        <v>46178</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="14"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="21">
-        <v>46179</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
-        <v>46180</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="21">
-        <v>46181</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
-        <v>46182</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
-        <v>46183</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="21">
-        <v>46184</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="21">
-        <v>46185</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="21">
-        <v>46186</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="14"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="21">
-        <v>46187</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="21">
-        <v>46188</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="21">
-        <v>46189</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="21">
-        <v>46190</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="14"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="21">
-        <v>46191</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="14"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="21">
-        <v>46192</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="14"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="21">
-        <v>46193</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="14"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="21">
-        <v>46194</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="14"/>
-      <c r="K24" s="1"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="21">
-        <v>46195</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="14"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="21">
-        <v>46196</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="14"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="21">
-        <v>46197</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="14"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="21">
-        <v>46198</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="14"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="21">
-        <v>46199</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="14"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="21">
-        <v>46200</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="24">
-        <v>9665</v>
-      </c>
-      <c r="D30" s="24">
-        <v>325</v>
-      </c>
-      <c r="E30" s="24">
-        <v>600</v>
-      </c>
-      <c r="F30" s="24">
-        <f>9665+325+600</f>
-        <v>10590</v>
-      </c>
-      <c r="G30" s="14"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="21">
-        <v>46201</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="24">
-        <f>4640+8560</f>
-        <v>13200</v>
-      </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24">
-        <f>170+40+30+200+350+200+180+345+90+45+390+120</f>
-        <v>2160</v>
-      </c>
-      <c r="F31" s="24">
-        <f>IF(SUM(C31:E31)=0,0,SUM(C31:E31))</f>
-        <v>15360</v>
-      </c>
-      <c r="G31" s="14"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="21">
-        <v>46202</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="24">
-        <v>3515</v>
-      </c>
-      <c r="D32" s="24">
-        <v>105</v>
-      </c>
-      <c r="E32" s="24">
-        <v>695</v>
-      </c>
-      <c r="F32" s="24">
-        <f>IF(SUM(C32:E32)=0,0,SUM(C32:E32))</f>
-        <v>4315</v>
-      </c>
-      <c r="G32" s="14"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="21">
-        <v>46203</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="24">
-        <v>3900</v>
-      </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24">
-        <v>1355</v>
-      </c>
-      <c r="F33" s="24">
-        <f>IF(SUM(C33:E33)=0,0,SUM(C33:E33))</f>
-        <v>5255</v>
-      </c>
-      <c r="G33" s="14"/>
-    </row>
-    <row r="34" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36">
-        <f>SUM(C4:C33)</f>
-        <v>30280</v>
-      </c>
-      <c r="D34" s="36">
-        <f>SUM(D4:D33)</f>
-        <v>430</v>
-      </c>
-      <c r="E34" s="36">
-        <f>SUM(E4:E33)</f>
-        <v>4810</v>
-      </c>
-      <c r="F34" s="36">
-        <f>SUM(F4:F33)</f>
-        <v>35520</v>
-      </c>
-      <c r="G34" s="8"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C35" s="22"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFED7D31"/>
-  </sheetPr>
-  <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="47">
-        <v>46180</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="33">
-        <v>10100</v>
-      </c>
-      <c r="H4" s="14"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="47">
-        <v>46181</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="33">
-        <v>3200</v>
-      </c>
-      <c r="H5" s="14"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="47">
-        <v>46182</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="33">
-        <v>8576</v>
-      </c>
-      <c r="H6" s="14"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="47">
-        <v>46183</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="33">
-        <v>3000</v>
-      </c>
-      <c r="H7" s="14"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="47">
-        <v>46184</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="33">
-        <v>1675</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="47">
-        <v>46185</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="33">
-        <v>14400</v>
-      </c>
-      <c r="H9" s="14"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="47">
-        <v>46186</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="33">
-        <v>250</v>
-      </c>
-      <c r="H10" s="14"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="47">
-        <v>46187</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="33">
-        <v>100</v>
-      </c>
-      <c r="H11" s="14"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="47">
-        <v>46188</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="33">
-        <v>5995</v>
-      </c>
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="47">
-        <v>46189</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="33">
-        <f>630+310+8406+660</f>
-        <v>10006</v>
-      </c>
-      <c r="H13" s="14"/>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="47">
-        <v>46190</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="33">
-        <f>230+4850+1670+3900+565</f>
-        <v>11215</v>
-      </c>
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="47">
-        <v>46191</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="33">
-        <f>600+1260</f>
-        <v>1860</v>
-      </c>
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="47">
-        <v>46190</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="33">
-        <v>7806</v>
-      </c>
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="47">
-        <v>46193</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="33">
-        <f>260+1375+6431</f>
-        <v>8066</v>
-      </c>
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="47">
-        <v>46194</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="33">
-        <f>4085+260</f>
-        <v>4345</v>
-      </c>
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="47">
-        <v>46195</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="33">
-        <f>450+5485</f>
-        <v>5935</v>
-      </c>
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="47">
-        <v>46196</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="33">
-        <f>500+400+2250</f>
-        <v>3150</v>
-      </c>
-      <c r="H20" s="14"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="47">
-        <v>46197</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="33">
-        <f>2060+910+5250</f>
-        <v>8220</v>
-      </c>
-      <c r="H21" s="14"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="47">
-        <v>46198</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="33">
-        <v>6500</v>
-      </c>
-      <c r="H22" s="14"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="47">
-        <v>46199</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="33">
-        <f>3920+3150</f>
-        <v>7070</v>
-      </c>
-      <c r="H23" s="14"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="47">
-        <v>46200</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="25">
-        <v>1635</v>
-      </c>
-      <c r="H24" s="14"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="47">
-        <v>46201</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D25" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="25">
-        <v>13425</v>
-      </c>
-      <c r="H25" s="14"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="47">
-        <v>46201</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D26" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="25">
-        <v>5895</v>
-      </c>
-      <c r="H26" s="14"/>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="47">
-        <v>46201</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="25">
-        <v>225</v>
-      </c>
-      <c r="H27" s="14"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="47">
-        <v>46201</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="25">
-        <v>50</v>
-      </c>
-      <c r="H28" s="14"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="47">
-        <v>46201</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C29" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="25">
-        <v>925</v>
-      </c>
-      <c r="H29" s="14"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="47">
-        <v>46202</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="25">
-        <v>450</v>
-      </c>
-      <c r="H30" s="14"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="47">
-        <v>46202</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="25">
-        <v>8440</v>
-      </c>
-      <c r="H31" s="14"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="47">
-        <v>46202</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="25">
-        <v>1046</v>
-      </c>
-      <c r="H32" s="14"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="47">
-        <v>46202</v>
-      </c>
-      <c r="B33" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="25">
-        <v>8000</v>
-      </c>
-      <c r="H33" s="28"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="47">
-        <v>46203</v>
-      </c>
-      <c r="B34" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="25">
-        <v>1700</v>
-      </c>
-      <c r="H34" s="14"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="47">
-        <v>46203</v>
-      </c>
-      <c r="B35" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="D35" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="25">
-        <v>350</v>
-      </c>
-      <c r="H35" s="14"/>
-    </row>
-    <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A36" s="58"/>
-      <c r="B36" s="29"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="59">
-        <f>SUM(G4:G35)</f>
-        <v>163610</v>
-      </c>
-      <c r="H36" s="38" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="58"/>
-      <c r="B37" s="29" t="str">
-        <f t="shared" ref="B37:B39" si="0">IF(A37="","",TEXT(A37,"dddd"))</f>
-        <v/>
-      </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="58"/>
-      <c r="B38" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFF6B6B"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="36.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
-        <v>158</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-    </row>
-    <row r="3" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47">
-        <v>46218</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="30">
-        <v>890</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47">
-        <v>46195</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="C5" s="30">
-        <v>890</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="47">
-        <v>46200</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="30">
-        <f>690+200</f>
-        <v>890</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47">
-        <v>46200</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="30">
-        <v>150</v>
-      </c>
-      <c r="D7" s="37"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="47">
-        <v>46201</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="30">
-        <v>80</v>
-      </c>
-      <c r="D8" s="37"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="47">
-        <v>46201</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="30">
-        <v>140</v>
-      </c>
-      <c r="D9" s="37"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="47">
-        <v>46201</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="30">
-        <v>55</v>
-      </c>
-      <c r="D10" s="37"/>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="47">
-        <v>46201</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="30">
-        <v>120</v>
-      </c>
-      <c r="D11" s="37"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="47">
-        <v>46201</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="30">
-        <v>190</v>
-      </c>
-      <c r="D12" s="37"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="47">
-        <v>46202</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" s="30">
-        <v>50</v>
-      </c>
-      <c r="D13" s="37"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="47">
-        <v>46202</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="30">
-        <v>180</v>
-      </c>
-      <c r="D14" s="37"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="47">
-        <v>46202</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="30">
-        <v>3800</v>
-      </c>
-      <c r="D15" s="37"/>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="47">
-        <v>46202</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="30">
-        <v>150</v>
-      </c>
-      <c r="D16" s="37"/>
-    </row>
-    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="30">
-        <v>18000</v>
-      </c>
-      <c r="D17" s="32"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" s="30">
-        <v>1500</v>
-      </c>
-      <c r="D18" s="32"/>
-    </row>
-    <row r="19" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="C19" s="30">
-        <v>2000</v>
-      </c>
-      <c r="D19" s="32"/>
-    </row>
-    <row r="20" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="23">
-        <f>SUM(C4:C19)</f>
-        <v>29085</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="C36" s="1"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="C38" s="1"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="C39" s="1"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="C40" s="1"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="9">
-        <f>SUM(C6:C40)</f>
-        <v>56390</v>
-      </c>
-      <c r="D42" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FFFF69B4"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="5" width="12" customWidth="1"/>
-    <col min="6" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="66" t="s">
-        <v>191</v>
-      </c>
-      <c r="G7" s="66"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-    </row>
-    <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="16">
-        <v>46174</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="14"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="16">
-        <v>46175</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="14"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="16">
-        <v>46176</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="14"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="16">
-        <v>46177</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="14"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="16">
-        <v>46178</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="14"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="16">
-        <v>46179</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="14"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
-        <v>46180</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="41">
-        <v>4150</v>
-      </c>
-      <c r="J17" s="19"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
-        <v>46181</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="41">
-        <v>3885</v>
-      </c>
-      <c r="J18" s="19"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
-        <v>46182</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="41">
-        <v>2685</v>
-      </c>
-      <c r="J19" s="49" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
-        <v>46183</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="41">
-        <v>2193</v>
-      </c>
-      <c r="J20" s="49" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
-        <v>46184</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="41">
-        <v>6445</v>
-      </c>
-      <c r="J21" s="48"/>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
-        <v>46185</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="41">
-        <v>8050</v>
-      </c>
-      <c r="J22" s="48"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
-        <v>46186</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="41">
-        <v>11755</v>
-      </c>
-      <c r="J23" s="48"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
-        <v>46187</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="41">
-        <v>6955</v>
-      </c>
-      <c r="J24" s="48"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="16">
-        <v>46188</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="41">
-        <v>10900</v>
-      </c>
-      <c r="J25" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="L25" s="1"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="16">
-        <v>46189</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="41">
-        <v>7150</v>
-      </c>
-      <c r="J26" s="48"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="16">
-        <v>46190</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="41">
-        <v>10020</v>
-      </c>
-      <c r="J27" s="48"/>
-      <c r="L27" s="1"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="16">
-        <v>46191</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="41">
-        <v>8550</v>
-      </c>
-      <c r="J28" s="48"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="16">
-        <v>46192</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="41">
-        <v>5155</v>
-      </c>
-      <c r="J29" s="48"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
-        <v>46193</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="41">
-        <v>9100</v>
-      </c>
-      <c r="J30" s="48"/>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
-        <v>46194</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="41">
-        <v>11850</v>
-      </c>
-      <c r="J31" s="48"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="16">
-        <v>46195</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="41">
-        <v>10700</v>
-      </c>
-      <c r="J32" s="49" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="16">
-        <v>46196</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="41">
-        <v>9700</v>
-      </c>
-      <c r="J33" s="48"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
-        <v>46197</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="41">
-        <v>11000</v>
-      </c>
-      <c r="J34" s="48"/>
-    </row>
-    <row r="35" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="16">
-        <v>46198</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="41">
-        <v>15032</v>
-      </c>
-      <c r="J35" s="48"/>
-    </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16">
-        <v>46199</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="41">
-        <v>19573</v>
-      </c>
-      <c r="J36" s="49" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="16">
-        <v>46200</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="49">
-        <v>9665</v>
-      </c>
-      <c r="D37" s="49">
-        <v>600</v>
-      </c>
-      <c r="E37" s="49">
-        <v>325</v>
-      </c>
-      <c r="F37" s="26">
-        <v>1635</v>
-      </c>
-      <c r="G37" s="26">
-        <f>890+150</f>
-        <v>1040</v>
-      </c>
-      <c r="H37" s="26">
-        <v>125</v>
-      </c>
-      <c r="I37" s="41">
-        <v>13390</v>
-      </c>
-      <c r="J37" s="20" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="16">
-        <v>46201</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="49">
-        <f>4640+8560</f>
-        <v>13200</v>
-      </c>
-      <c r="D38" s="30">
-        <f>170+40+30+200+350+200+180+345+90+45+390+120</f>
-        <v>2160</v>
-      </c>
-      <c r="E38" s="30"/>
-      <c r="F38" s="26">
-        <f>845+300+170</f>
-        <v>1315</v>
-      </c>
-      <c r="G38" s="26">
-        <f>140+55+120+270</f>
-        <v>585</v>
-      </c>
-      <c r="H38" s="26">
-        <f>30+140+30+30+15+10+20+20+100</f>
-        <v>395</v>
-      </c>
-      <c r="I38" s="41">
-        <v>17655</v>
-      </c>
-      <c r="J38" s="20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="16">
-        <v>46202</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" s="30">
-        <v>2070</v>
-      </c>
-      <c r="D39" s="30">
-        <f>215+235+80+165</f>
-        <v>695</v>
-      </c>
-      <c r="E39" s="30">
-        <v>105</v>
-      </c>
-      <c r="F39" s="26">
-        <f>450+9450</f>
-        <v>9900</v>
-      </c>
-      <c r="G39" s="26">
-        <f>150+3800+180+50</f>
-        <v>4180</v>
-      </c>
-      <c r="H39" s="26">
-        <f>200+15+250+100+100+100+100</f>
-        <v>865</v>
-      </c>
-      <c r="I39" s="41">
-        <f>SUM(C39:H39)</f>
-        <v>17815</v>
-      </c>
-      <c r="J39" s="20" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="16">
-        <v>46203</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" s="30">
-        <v>3965</v>
-      </c>
-      <c r="D40" s="30">
-        <f>245+80+425+100+175+330</f>
-        <v>1355</v>
-      </c>
-      <c r="E40" s="30"/>
-      <c r="F40" s="26">
-        <f>1700+10000+350</f>
-        <v>12050</v>
-      </c>
-      <c r="G40" s="26">
-        <f>4065+300+100+85</f>
-        <v>4550</v>
-      </c>
-      <c r="H40" s="26">
-        <f>100+200+50+15+110+115+100+100+10</f>
-        <v>800</v>
-      </c>
-      <c r="I40" s="41">
-        <f>SUM(C40:H40)</f>
-        <v>22720</v>
-      </c>
-      <c r="J40" s="14"/>
-    </row>
-    <row r="41" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I41" s="71">
-        <f>SUM(I17:I40)</f>
-        <v>246428</v>
-      </c>
-      <c r="J41" s="38" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="50" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I50">
-        <f>65134+150605+27305</f>
-        <v>243044</v>
-      </c>
-    </row>
-    <row r="53" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I53">
-        <f>243044-246428</f>
-        <v>-3384</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="F7:G8"/>
-  </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup scale="56" fitToHeight="0" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF808080"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:V48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4737,31 +2355,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65"/>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
+      <c r="A1" s="72"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C2" s="69" t="s">
-        <v>156</v>
-      </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
+      <c r="C2" s="78" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
     </row>
     <row r="5" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -4789,80 +2407,74 @@
         <v>36</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="67" t="s">
-        <v>142</v>
-      </c>
-      <c r="V5" s="68"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
-        <v>1</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="41">
-        <f>50+15+50+80+20+10+30+15</f>
-        <v>270</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="H6" s="26"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="U6" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="V6" s="30" t="s">
-        <v>94</v>
-      </c>
+      <c r="U5" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="V5" s="77"/>
+    </row>
+    <row r="6" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15">
+        <v>11500</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="U6" s="69"/>
+      <c r="V6" s="70"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="25"/>
       <c r="E7" s="26"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="26"/>
+      <c r="F7" s="41">
+        <f>50+15+50+80+20+10+30+15</f>
+        <v>270</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>190</v>
+      </c>
       <c r="H7" s="26"/>
-      <c r="I7" s="30">
-        <v>5050</v>
+      <c r="I7" s="65">
+        <v>6500</v>
       </c>
       <c r="J7" s="30"/>
-      <c r="K7" s="30" t="s">
-        <v>195</v>
-      </c>
+      <c r="K7" s="30"/>
       <c r="U7" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="V7" s="30">
-        <v>1665</v>
+        <v>147</v>
+      </c>
+      <c r="V7" s="30" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C8" s="30"/>
       <c r="D8" s="25"/>
@@ -4871,25 +2483,25 @@
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
       <c r="I8" s="30">
-        <v>5000</v>
+        <v>5050</v>
       </c>
       <c r="J8" s="30"/>
       <c r="K8" s="30" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U8" s="30" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="V8" s="30">
-        <v>300</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="25"/>
@@ -4902,21 +2514,21 @@
       </c>
       <c r="J9" s="30"/>
       <c r="K9" s="30" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U9" s="30" t="s">
         <v>143</v>
       </c>
       <c r="V9" s="30">
-        <v>4104</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="25"/>
@@ -4925,25 +2537,25 @@
       <c r="G10" s="26"/>
       <c r="H10" s="26"/>
       <c r="I10" s="30">
-        <v>6120</v>
+        <v>5000</v>
       </c>
       <c r="J10" s="30"/>
       <c r="K10" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="U10" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="U10" s="30" t="s">
-        <v>150</v>
-      </c>
       <c r="V10" s="30">
-        <v>2000</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="25"/>
@@ -4951,58 +2563,45 @@
       <c r="F11" s="41"/>
       <c r="G11" s="26"/>
       <c r="H11" s="26"/>
-      <c r="I11" s="73">
-        <v>2750</v>
+      <c r="I11" s="30">
+        <v>6120</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30" t="s">
-        <v>195</v>
+        <v>141</v>
       </c>
       <c r="U11" s="30" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="V11" s="30">
-        <v>9000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="14">
-        <v>7</v>
-      </c>
+      <c r="A12" s="14"/>
       <c r="B12" s="30" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="C12" s="30"/>
       <c r="D12" s="25"/>
       <c r="E12" s="26"/>
-      <c r="F12" s="41">
-        <f>150+120</f>
-        <v>270</v>
-      </c>
+      <c r="F12" s="41"/>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
-      <c r="I12" s="73">
-        <v>3000</v>
-      </c>
-      <c r="J12" s="30">
-        <v>-520</v>
-      </c>
-      <c r="K12" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="U12" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="V12" s="30">
-        <v>1290</v>
-      </c>
+      <c r="I12" s="30">
+        <v>1660</v>
+      </c>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C13" s="30"/>
       <c r="D13" s="25"/>
@@ -5010,54 +2609,58 @@
       <c r="F13" s="41"/>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
-      <c r="I13" s="30">
-        <v>3675</v>
+      <c r="I13" s="66">
+        <v>2750</v>
       </c>
       <c r="J13" s="30"/>
       <c r="K13" s="30" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="U13" s="30" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="V13" s="30">
-        <v>1500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="25"/>
       <c r="E14" s="26"/>
       <c r="F14" s="41">
-        <f>200+30+15+200+15+20+20+70+87+25+10+10+30+355</f>
-        <v>1087</v>
+        <f>150+120</f>
+        <v>270</v>
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
-      <c r="I14" s="70">
+      <c r="I14" s="66">
         <v>3000</v>
       </c>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
+      <c r="J14" s="30">
+        <v>-520</v>
+      </c>
+      <c r="K14" s="30" t="s">
+        <v>193</v>
+      </c>
       <c r="U14" s="30" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="V14" s="30">
-        <v>6120</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C15" s="30"/>
       <c r="D15" s="25"/>
@@ -5066,137 +2669,168 @@
       <c r="G15" s="26"/>
       <c r="H15" s="26"/>
       <c r="I15" s="30">
-        <v>8350</v>
+        <v>3675</v>
       </c>
       <c r="J15" s="30"/>
       <c r="K15" s="30" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="U15" s="30" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="V15" s="30">
-        <v>8350</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="25"/>
       <c r="E16" s="26"/>
-      <c r="F16" s="41"/>
+      <c r="F16" s="41">
+        <f>200+30+15+200+15+20+20+70+87+25+10+10+30+355</f>
+        <v>1087</v>
+      </c>
       <c r="G16" s="26"/>
       <c r="H16" s="26"/>
-      <c r="I16" s="30">
-        <v>9000</v>
+      <c r="I16" s="63">
+        <v>6500</v>
       </c>
       <c r="J16" s="30"/>
-      <c r="K16" s="30" t="s">
-        <v>142</v>
-      </c>
+      <c r="K16" s="30"/>
       <c r="U16" s="30" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="V16" s="30">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>6120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="25"/>
       <c r="E17" s="26"/>
-      <c r="F17" s="41">
-        <v>400</v>
-      </c>
+      <c r="F17" s="41"/>
       <c r="G17" s="26"/>
       <c r="H17" s="26"/>
       <c r="I17" s="30">
-        <v>1770</v>
+        <v>8350</v>
       </c>
       <c r="J17" s="30"/>
       <c r="K17" s="30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="O17" t="s">
+        <v>104</v>
+      </c>
+      <c r="U17" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="V17" s="30">
+        <v>8350</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C18" s="30"/>
       <c r="D18" s="25"/>
       <c r="E18" s="26"/>
-      <c r="F18" s="41">
-        <v>400</v>
-      </c>
+      <c r="F18" s="41"/>
       <c r="G18" s="26"/>
       <c r="H18" s="26"/>
-      <c r="I18" s="74">
-        <v>600</v>
+      <c r="I18" s="30">
+        <v>9000</v>
       </c>
       <c r="J18" s="30"/>
       <c r="K18" s="30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="N18">
+        <v>150</v>
+      </c>
+      <c r="O18" s="79">
+        <v>46192</v>
+      </c>
+      <c r="U18" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="V18" s="30">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C19" s="30"/>
       <c r="D19" s="25"/>
       <c r="E19" s="26"/>
-      <c r="F19" s="41"/>
+      <c r="F19" s="41">
+        <v>400</v>
+      </c>
       <c r="G19" s="26"/>
       <c r="H19" s="26"/>
-      <c r="I19" s="73">
-        <v>1000</v>
+      <c r="I19" s="30">
+        <v>1770</v>
       </c>
       <c r="J19" s="30"/>
       <c r="K19" s="30" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="N19">
+        <v>55</v>
+      </c>
+      <c r="O19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C20" s="30"/>
       <c r="D20" s="25"/>
       <c r="E20" s="26"/>
-      <c r="F20" s="41"/>
+      <c r="F20" s="41">
+        <v>400</v>
+      </c>
       <c r="G20" s="26"/>
       <c r="H20" s="26"/>
-      <c r="I20" s="30">
-        <f>6000+1000+1500+500</f>
-        <v>9000</v>
+      <c r="I20" s="67">
+        <v>600</v>
       </c>
       <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+      <c r="K20" s="30" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <v>14</v>
+      </c>
       <c r="B21" s="30" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="C21" s="30"/>
       <c r="D21" s="25"/>
@@ -5204,99 +2838,101 @@
       <c r="F21" s="41"/>
       <c r="G21" s="26"/>
       <c r="H21" s="26"/>
-      <c r="I21" s="30">
-        <f>2750+1660</f>
-        <v>4410</v>
+      <c r="I21" s="68">
+        <v>1000</v>
       </c>
       <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K21" s="30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C22" s="30"/>
       <c r="D22" s="25"/>
       <c r="E22" s="26"/>
-      <c r="F22" s="41">
-        <v>120</v>
-      </c>
+      <c r="F22" s="41"/>
       <c r="G22" s="26"/>
       <c r="H22" s="26"/>
-      <c r="I22" s="72"/>
+      <c r="I22" s="30">
+        <f>6000+1000+1500+500</f>
+        <v>9000</v>
+      </c>
       <c r="J22" s="30"/>
       <c r="K22" s="30"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="14">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="14"/>
+      <c r="B23" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="30"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="30">
+        <f>2750+1660</f>
+        <v>4410</v>
+      </c>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <v>16</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="30"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="41">
+        <v>120</v>
+      </c>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="65">
+        <v>3685</v>
+      </c>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="14">
         <v>17</v>
       </c>
-      <c r="B23" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="39">
-        <v>130</v>
-      </c>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30">
-        <v>1330</v>
-      </c>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>18</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="39">
-        <f>500</f>
-        <v>500</v>
-      </c>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="14">
-        <v>19</v>
-      </c>
       <c r="B25" s="30" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="28"/>
       <c r="E25" s="30"/>
-      <c r="F25" s="39"/>
+      <c r="F25" s="39">
+        <v>130</v>
+      </c>
       <c r="G25" s="30"/>
       <c r="H25" s="30"/>
       <c r="I25" s="30">
-        <v>1665</v>
+        <v>1330</v>
       </c>
       <c r="J25" s="30"/>
       <c r="K25" s="30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="14">
-        <v>20</v>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>18</v>
       </c>
       <c r="B26" s="30" t="s">
         <v>144</v>
@@ -5304,23 +2940,24 @@
       <c r="C26" s="30"/>
       <c r="D26" s="28"/>
       <c r="E26" s="30"/>
-      <c r="F26" s="39"/>
+      <c r="F26" s="39">
+        <f>500</f>
+        <v>500</v>
+      </c>
       <c r="G26" s="30"/>
       <c r="H26" s="30"/>
-      <c r="I26" s="30">
-        <v>300</v>
+      <c r="I26" s="65">
+        <v>8305</v>
       </c>
       <c r="J26" s="30"/>
-      <c r="K26" s="30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K26" s="30"/>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C27" s="30"/>
       <c r="D27" s="28"/>
@@ -5329,19 +2966,19 @@
       <c r="G27" s="30"/>
       <c r="H27" s="30"/>
       <c r="I27" s="30">
-        <v>4104</v>
+        <v>1665</v>
       </c>
       <c r="J27" s="30"/>
       <c r="K27" s="30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C28" s="30"/>
       <c r="D28" s="28"/>
@@ -5350,19 +2987,19 @@
       <c r="G28" s="30"/>
       <c r="H28" s="30"/>
       <c r="I28" s="30">
-        <v>1290</v>
+        <v>300</v>
       </c>
       <c r="J28" s="30"/>
       <c r="K28" s="30" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" s="14">
+        <v>21</v>
+      </c>
+      <c r="B29" s="30" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="14">
-        <v>23</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>150</v>
       </c>
       <c r="C29" s="30"/>
       <c r="D29" s="28"/>
@@ -5371,42 +3008,40 @@
       <c r="G29" s="30"/>
       <c r="H29" s="30"/>
       <c r="I29" s="30">
-        <v>2000</v>
+        <v>4104</v>
       </c>
       <c r="J29" s="30"/>
       <c r="K29" s="30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C30" s="30"/>
       <c r="D30" s="28"/>
       <c r="E30" s="30"/>
-      <c r="F30" s="39">
-        <v>120</v>
-      </c>
+      <c r="F30" s="39"/>
       <c r="G30" s="30"/>
       <c r="H30" s="30"/>
       <c r="I30" s="30">
-        <v>3000</v>
+        <v>1290</v>
       </c>
       <c r="J30" s="30"/>
       <c r="K30" s="30" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C31" s="30"/>
       <c r="D31" s="28"/>
@@ -5415,51 +3050,93 @@
       <c r="G31" s="30"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="J31" s="30"/>
       <c r="K31" s="30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="30">
-        <v>1500</v>
+        <v>197</v>
+      </c>
+      <c r="C32" s="30"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="39">
+        <v>120</v>
+      </c>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="68">
+        <v>9765</v>
       </c>
       <c r="J32" s="30"/>
       <c r="K32" s="30"/>
     </row>
-    <row r="33" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I33" s="23">
-        <f>SUM(I6:I32)</f>
-        <v>86914</v>
-      </c>
-      <c r="J33" s="38" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="2">
+    <row r="33" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <v>25</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="30"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="68">
+        <v>4000</v>
+      </c>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <v>26</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="30">
+        <v>1500</v>
+      </c>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+    </row>
+    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I35" s="23">
+        <f>SUM(I7:I34)</f>
+        <v>117329</v>
+      </c>
+      <c r="J35" s="38" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="2">
         <v>46203</v>
       </c>
-      <c r="C46" t="s">
-        <v>166</v>
-      </c>
-      <c r="D46" t="s">
-        <v>196</v>
+      <c r="C48" t="s">
+        <v>164</v>
+      </c>
+      <c r="D48" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -5469,7 +3146,7 @@
     <mergeCell ref="C2:G3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="خطأ" error="يرجى اختيار موظف من القائمة" sqref="B6:B23" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="خطأ" error="يرجى اختيار موظف من القائمة" sqref="B7:B25" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>INDIRECT("الموظفين!$B$4:$B$23")</formula1>
     </dataValidation>
   </dataValidations>
@@ -5478,7 +3155,2290 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+      <c r="A1" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="21">
+        <v>46174</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="21">
+        <v>46175</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="21">
+        <v>46176</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="21">
+        <v>46177</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="21">
+        <v>46178</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="21">
+        <v>46179</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="21">
+        <v>46180</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="21">
+        <v>46181</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="21">
+        <v>46182</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="21">
+        <v>46183</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="21">
+        <v>46184</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="21">
+        <v>46185</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="21">
+        <v>46186</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="21">
+        <v>46187</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="21">
+        <v>46188</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="21">
+        <v>46189</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="21">
+        <v>46190</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="21">
+        <v>46191</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="21">
+        <v>46192</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="21">
+        <v>46193</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="21">
+        <v>46194</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="14"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="21">
+        <v>46195</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="21">
+        <v>46196</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="14"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="21">
+        <v>46197</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="21">
+        <v>46198</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="14"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="21">
+        <v>46199</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="21">
+        <v>46200</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="24">
+        <v>9665</v>
+      </c>
+      <c r="D30" s="24">
+        <v>325</v>
+      </c>
+      <c r="E30" s="24">
+        <v>600</v>
+      </c>
+      <c r="F30" s="24">
+        <f>9665+325+600</f>
+        <v>10590</v>
+      </c>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="21">
+        <v>46201</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="24">
+        <f>4640+8560</f>
+        <v>13200</v>
+      </c>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24">
+        <f>170+40+30+200+350+200+180+345+90+45+390+120</f>
+        <v>2160</v>
+      </c>
+      <c r="F31" s="24">
+        <f>IF(SUM(C31:E31)=0,0,SUM(C31:E31))</f>
+        <v>15360</v>
+      </c>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="21">
+        <v>46202</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="24">
+        <v>3515</v>
+      </c>
+      <c r="D32" s="24">
+        <v>105</v>
+      </c>
+      <c r="E32" s="24">
+        <v>695</v>
+      </c>
+      <c r="F32" s="24">
+        <f>IF(SUM(C32:E32)=0,0,SUM(C32:E32))</f>
+        <v>4315</v>
+      </c>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="21">
+        <v>46203</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="24">
+        <v>3900</v>
+      </c>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24">
+        <v>1355</v>
+      </c>
+      <c r="F33" s="24">
+        <f>IF(SUM(C33:E33)=0,0,SUM(C33:E33))</f>
+        <v>5255</v>
+      </c>
+      <c r="G33" s="14"/>
+    </row>
+    <row r="34" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36">
+        <f>SUM(C4:C33)</f>
+        <v>30280</v>
+      </c>
+      <c r="D34" s="36">
+        <f>SUM(D4:D33)</f>
+        <v>430</v>
+      </c>
+      <c r="E34" s="36">
+        <f>SUM(E4:E33)</f>
+        <v>4810</v>
+      </c>
+      <c r="F34" s="36">
+        <f>SUM(F4:F33)</f>
+        <v>35520</v>
+      </c>
+      <c r="G34" s="8"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C35" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF69B4"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="5" width="12" customWidth="1"/>
+    <col min="6" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.25">
+      <c r="A1" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="75" t="s">
+        <v>189</v>
+      </c>
+      <c r="G7" s="75"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+    </row>
+    <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>46174</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="16">
+        <v>46175</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>46176</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="16">
+        <v>46177</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="16">
+        <v>46178</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>46179</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="16">
+        <v>46180</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>46181</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="41">
+        <v>3885</v>
+      </c>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="16">
+        <v>46182</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="41">
+        <v>2685</v>
+      </c>
+      <c r="J19" s="49" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="16">
+        <v>46183</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="41">
+        <v>2193</v>
+      </c>
+      <c r="J20" s="49" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="16">
+        <v>46184</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="41">
+        <v>6445</v>
+      </c>
+      <c r="J21" s="48"/>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="16">
+        <v>46185</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="41">
+        <v>8050</v>
+      </c>
+      <c r="J22" s="48"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
+        <v>46186</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="41">
+        <v>11755</v>
+      </c>
+      <c r="J23" s="48"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>46187</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="41">
+        <v>6955</v>
+      </c>
+      <c r="J24" s="48"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="16">
+        <v>46188</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="41">
+        <v>10900</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="16">
+        <v>46189</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="41">
+        <v>7150</v>
+      </c>
+      <c r="J26" s="48"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <v>46190</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="41">
+        <v>10020</v>
+      </c>
+      <c r="J27" s="48"/>
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="16">
+        <v>46191</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="41">
+        <v>8550</v>
+      </c>
+      <c r="J28" s="48"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="16">
+        <v>46192</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="41">
+        <v>5155</v>
+      </c>
+      <c r="J29" s="48"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="16">
+        <v>46193</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="41">
+        <v>9100</v>
+      </c>
+      <c r="J30" s="48"/>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="16">
+        <v>46194</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="41">
+        <v>11850</v>
+      </c>
+      <c r="J31" s="48"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="16">
+        <v>46195</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="41">
+        <v>10700</v>
+      </c>
+      <c r="J32" s="49" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="16">
+        <v>46196</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="41">
+        <v>9700</v>
+      </c>
+      <c r="J33" s="48"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="16">
+        <v>46197</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="41">
+        <v>11000</v>
+      </c>
+      <c r="J34" s="48"/>
+    </row>
+    <row r="35" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16">
+        <v>46198</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="41">
+        <v>15032</v>
+      </c>
+      <c r="J35" s="48"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16">
+        <v>46199</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="41">
+        <v>19573</v>
+      </c>
+      <c r="J36" s="49" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="16">
+        <v>46200</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="49">
+        <v>9665</v>
+      </c>
+      <c r="D37" s="49">
+        <v>600</v>
+      </c>
+      <c r="E37" s="49">
+        <v>325</v>
+      </c>
+      <c r="F37" s="26">
+        <v>1635</v>
+      </c>
+      <c r="G37" s="26">
+        <f>890+150</f>
+        <v>1040</v>
+      </c>
+      <c r="H37" s="26">
+        <v>125</v>
+      </c>
+      <c r="I37" s="41">
+        <v>13390</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="16">
+        <v>46201</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="49">
+        <f>4640+8560</f>
+        <v>13200</v>
+      </c>
+      <c r="D38" s="30">
+        <f>170+40+30+200+350+200+180+345+90+45+390+120</f>
+        <v>2160</v>
+      </c>
+      <c r="E38" s="30"/>
+      <c r="F38" s="26">
+        <f>845+300+170</f>
+        <v>1315</v>
+      </c>
+      <c r="G38" s="26">
+        <f>140+55+120+270</f>
+        <v>585</v>
+      </c>
+      <c r="H38" s="26">
+        <f>30+140+30+30+15+10+20+20+100</f>
+        <v>395</v>
+      </c>
+      <c r="I38" s="41">
+        <v>17655</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="16">
+        <v>46202</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="30">
+        <v>2070</v>
+      </c>
+      <c r="D39" s="30">
+        <f>215+235+80+165</f>
+        <v>695</v>
+      </c>
+      <c r="E39" s="30">
+        <v>105</v>
+      </c>
+      <c r="F39" s="26">
+        <f>450+9450</f>
+        <v>9900</v>
+      </c>
+      <c r="G39" s="26">
+        <f>150+3800+180+50</f>
+        <v>4180</v>
+      </c>
+      <c r="H39" s="26">
+        <f>200+15+250+100+100+100+100</f>
+        <v>865</v>
+      </c>
+      <c r="I39" s="41">
+        <f>SUM(C39:H39)</f>
+        <v>17815</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>46203</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="30">
+        <v>3965</v>
+      </c>
+      <c r="D40" s="30">
+        <f>245+80+425+100+175+330</f>
+        <v>1355</v>
+      </c>
+      <c r="E40" s="30"/>
+      <c r="F40" s="26">
+        <f>1700+10000+350</f>
+        <v>12050</v>
+      </c>
+      <c r="G40" s="26">
+        <f>4065+300+100+85</f>
+        <v>4550</v>
+      </c>
+      <c r="H40" s="26">
+        <f>100+200+50+15+110+115+100+100+10</f>
+        <v>800</v>
+      </c>
+      <c r="I40" s="41">
+        <f>SUM(C40:H40)</f>
+        <v>22720</v>
+      </c>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I41" s="64">
+        <f>SUM(I17:I40)</f>
+        <v>242278</v>
+      </c>
+      <c r="J41" s="38" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I50">
+        <f>65134+150605+27305</f>
+        <v>243044</v>
+      </c>
+    </row>
+    <row r="53" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I53">
+        <f>243044-246428</f>
+        <v>-3384</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="F7:G8"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup scale="56" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFED7D31"/>
+  </sheetPr>
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A1" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="47">
+        <v>46180</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="33">
+        <v>10100</v>
+      </c>
+      <c r="H4" s="14"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="47">
+        <v>46181</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="33">
+        <v>3200</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="47">
+        <v>46182</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="33">
+        <v>8576</v>
+      </c>
+      <c r="H6" s="14"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="47">
+        <v>46183</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="33">
+        <v>3000</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="47">
+        <v>46184</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="33">
+        <v>1675</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="47">
+        <v>46185</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="33">
+        <v>14400</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="47">
+        <v>46186</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="33">
+        <v>250</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="47">
+        <v>46187</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="33">
+        <v>100</v>
+      </c>
+      <c r="H11" s="14"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="47">
+        <v>46188</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="33">
+        <v>5995</v>
+      </c>
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="47">
+        <v>46189</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="33">
+        <f>630+310+8406+660</f>
+        <v>10006</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="47">
+        <v>46190</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="33">
+        <f>230+4850+1670+3900+565</f>
+        <v>11215</v>
+      </c>
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="47">
+        <v>46191</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="33">
+        <f>600+1260</f>
+        <v>1860</v>
+      </c>
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="47">
+        <v>46190</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="33">
+        <v>7806</v>
+      </c>
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="47">
+        <v>46193</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="33">
+        <f>260+1375+6431</f>
+        <v>8066</v>
+      </c>
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="47">
+        <v>46194</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="33">
+        <f>4085+260</f>
+        <v>4345</v>
+      </c>
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="47">
+        <v>46195</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="33">
+        <f>450+5485</f>
+        <v>5935</v>
+      </c>
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="47">
+        <v>46196</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="33">
+        <f>500+400+2250</f>
+        <v>3150</v>
+      </c>
+      <c r="H20" s="14"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="47">
+        <v>46197</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="33">
+        <f>2060+910+5250</f>
+        <v>8220</v>
+      </c>
+      <c r="H21" s="14"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="47">
+        <v>46198</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="33">
+        <v>6500</v>
+      </c>
+      <c r="H22" s="14"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="47">
+        <v>46199</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="33">
+        <f>3920+3150</f>
+        <v>7070</v>
+      </c>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="47">
+        <v>46200</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="25">
+        <v>1635</v>
+      </c>
+      <c r="H24" s="14"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="47">
+        <v>46201</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="25">
+        <v>13425</v>
+      </c>
+      <c r="H25" s="14"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="47">
+        <v>46201</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="25">
+        <v>5895</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="47">
+        <v>46201</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="25">
+        <v>225</v>
+      </c>
+      <c r="H27" s="14"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="47">
+        <v>46201</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="25">
+        <v>50</v>
+      </c>
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="47">
+        <v>46201</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="25">
+        <v>925</v>
+      </c>
+      <c r="H29" s="14"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="47">
+        <v>46202</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="25">
+        <v>450</v>
+      </c>
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="47">
+        <v>46202</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="25">
+        <v>8440</v>
+      </c>
+      <c r="H31" s="14"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="47">
+        <v>46202</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="25">
+        <v>1046</v>
+      </c>
+      <c r="H32" s="14"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="47">
+        <v>46202</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="25">
+        <v>8000</v>
+      </c>
+      <c r="H33" s="28"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="47">
+        <v>46203</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="25">
+        <v>1700</v>
+      </c>
+      <c r="H34" s="14"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="47">
+        <v>46203</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="25">
+        <v>350</v>
+      </c>
+      <c r="H35" s="14"/>
+    </row>
+    <row r="36" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A36" s="58"/>
+      <c r="B36" s="29"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="59">
+        <f>SUM(G4:G35)</f>
+        <v>163610</v>
+      </c>
+      <c r="H36" s="38" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="58"/>
+      <c r="B37" s="29" t="str">
+        <f t="shared" ref="B37:B39" si="0">IF(A37="","",TEXT(A37,"dddd"))</f>
+        <v/>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="58"/>
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF6B6B"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
+      <c r="A1" s="74" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+    </row>
+    <row r="3" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="47">
+        <v>46218</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="30">
+        <v>890</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="47">
+        <v>46195</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="30">
+        <v>890</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="47">
+        <v>46200</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="30">
+        <f>690+200</f>
+        <v>890</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="47">
+        <v>46200</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="30">
+        <v>150</v>
+      </c>
+      <c r="D7" s="37"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="47">
+        <v>46201</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="30">
+        <v>80</v>
+      </c>
+      <c r="D8" s="37"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="47">
+        <v>46201</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="30">
+        <v>140</v>
+      </c>
+      <c r="D9" s="37"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="47">
+        <v>46201</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="30">
+        <v>55</v>
+      </c>
+      <c r="D10" s="37"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="47">
+        <v>46201</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="30">
+        <v>120</v>
+      </c>
+      <c r="D11" s="37"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="47">
+        <v>46201</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="30">
+        <v>190</v>
+      </c>
+      <c r="D12" s="37"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="47">
+        <v>46202</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="30">
+        <v>50</v>
+      </c>
+      <c r="D13" s="37"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="47">
+        <v>46202</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="30">
+        <v>180</v>
+      </c>
+      <c r="D14" s="37"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="47">
+        <v>46202</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="30">
+        <v>3800</v>
+      </c>
+      <c r="D15" s="37"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="47">
+        <v>46202</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="30">
+        <v>150</v>
+      </c>
+      <c r="D16" s="37"/>
+    </row>
+    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="30">
+        <v>18000</v>
+      </c>
+      <c r="D17" s="32"/>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="30">
+        <v>1500</v>
+      </c>
+      <c r="D18" s="32"/>
+    </row>
+    <row r="19" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="30">
+        <v>2000</v>
+      </c>
+      <c r="D19" s="32"/>
+    </row>
+    <row r="20" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="23">
+        <f>SUM(C4:C19)</f>
+        <v>29085</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="C33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="C34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="C35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="C38" s="1"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="C39" s="1"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="C40" s="1"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="9">
+        <f>SUM(C6:C40)</f>
+        <v>56390</v>
+      </c>
+      <c r="D42" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -5494,12 +5454,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -5519,15 +5479,15 @@
         <v>2085</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" s="28">
         <v>100</v>
@@ -5536,10 +5496,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>81</v>
+        <v>90</v>
+      </c>
+      <c r="B5" s="71" t="s">
+        <v>151</v>
       </c>
       <c r="C5" s="28">
         <v>25</v>
@@ -5548,10 +5508,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="28">
         <v>100</v>
@@ -5560,10 +5520,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>81</v>
+        <v>102</v>
+      </c>
+      <c r="B7" s="71" t="s">
+        <v>80</v>
       </c>
       <c r="C7" s="28">
         <v>70</v>
@@ -5572,10 +5532,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="71" t="s">
         <v>103</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>104</v>
       </c>
       <c r="C8" s="28">
         <v>20</v>
@@ -5584,10 +5544,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C9" s="62">
         <v>20</v>
@@ -5596,10 +5556,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" s="28">
         <v>20</v>
@@ -5608,10 +5568,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" s="28">
         <v>20</v>
@@ -5620,10 +5580,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C12" s="28">
         <v>30</v>
@@ -5632,10 +5592,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C13" s="62">
         <v>45</v>
@@ -5644,10 +5604,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>81</v>
+        <v>102</v>
+      </c>
+      <c r="B14" s="71" t="s">
+        <v>80</v>
       </c>
       <c r="C14" s="28">
         <v>20</v>
@@ -5657,10 +5617,10 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" s="28">
         <v>20</v>
@@ -5669,10 +5629,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" s="28">
         <v>30</v>
@@ -5681,10 +5641,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="28">
         <v>200</v>
@@ -5693,10 +5653,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C18" s="28">
         <v>250</v>
@@ -5705,10 +5665,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C19" s="28">
         <v>100</v>
@@ -5717,10 +5677,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>81</v>
+        <v>116</v>
+      </c>
+      <c r="B20" s="71" t="s">
+        <v>80</v>
       </c>
       <c r="C20" s="28">
         <v>15</v>
@@ -5729,30 +5689,30 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>104</v>
+        <v>116</v>
+      </c>
+      <c r="B21" s="71" t="s">
+        <v>103</v>
       </c>
       <c r="C21" s="25">
         <v>100</v>
       </c>
       <c r="D21" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22" s="25">
         <v>100</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5768,7 +5728,7 @@
         <v>46203</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="25">
         <v>200</v>
@@ -5779,8 +5739,8 @@
       <c r="A25" s="16">
         <v>46203</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>104</v>
+      <c r="B25" s="71" t="s">
+        <v>103</v>
       </c>
       <c r="C25" s="25">
         <v>50</v>
@@ -5791,8 +5751,8 @@
       <c r="A26" s="16">
         <v>46203</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>81</v>
+      <c r="B26" s="71" t="s">
+        <v>80</v>
       </c>
       <c r="C26" s="25">
         <v>25</v>
@@ -5804,7 +5764,7 @@
         <v>46203</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="25">
         <v>110</v>
@@ -5816,7 +5776,7 @@
         <v>46203</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C28" s="30">
         <v>115</v>
@@ -5828,7 +5788,7 @@
         <v>46203</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C29" s="25">
         <v>100</v>
@@ -5840,7 +5800,7 @@
         <v>46203</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C30" s="25">
         <v>100</v>
@@ -5852,13 +5812,13 @@
         <v>46203</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" s="25">
         <v>100</v>
       </c>
       <c r="D31" s="39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5955,6 +5915,150 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF50A280"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:G22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
+      <c r="A2" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="45">
+        <v>6</v>
+      </c>
+      <c r="B6" s="43">
+        <f>SUM('تقفيلة اليوم'!I17:I40)</f>
+        <v>242278</v>
+      </c>
+      <c r="C6" s="43">
+        <f>SUM('المشتريات اليومية'!G36)</f>
+        <v>163610</v>
+      </c>
+      <c r="D6" s="43">
+        <v>29085</v>
+      </c>
+      <c r="E6" s="43">
+        <f>SUM(الرواتب!I7:I34)</f>
+        <v>117329</v>
+      </c>
+      <c r="F6" s="43">
+        <f>SUM(E22)</f>
+        <v>-67746</v>
+      </c>
+      <c r="G6" s="44"/>
+    </row>
+    <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="80">
+        <f>SUM(C6:E6)</f>
+        <v>310024</v>
+      </c>
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="80">
+        <f>SUM(B6-E17)</f>
+        <v>-67746</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup scale="58" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -5976,16 +6080,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -6369,15 +6473,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">

--- a/Cafe 2M.xlsx
+++ b/Cafe 2M.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GHOST\OneDrive\سطح المكتب\cafe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF5C4E2-A920-46DE-A058-21F1FC740022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F675E2-1166-48DA-88CE-76AFE4C2EF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الموظفين" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="199">
   <si>
     <t>المشتريات اليومية</t>
   </si>
@@ -1149,14 +1149,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="26" fillId="6" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1168,8 +1170,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="26" fillId="6" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -1178,6 +1178,54 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9E1F2"/>
+          <bgColor rgb="FFD9E1F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
     </dxf>
@@ -1241,54 +1289,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9E1F2"/>
-          <bgColor rgb="FFD9E1F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1303,15 +1303,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A6F27E3D-FBAF-4743-A0A3-D8E2D9B03B04}" name="Table2" displayName="Table2" ref="A4:G6" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A6F27E3D-FBAF-4743-A0A3-D8E2D9B03B04}" name="Table2" displayName="Table2" ref="A4:G6" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A4:G6" xr:uid="{A6F27E3D-FBAF-4743-A0A3-D8E2D9B03B04}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{A998BA95-B09C-44A1-A227-B8F1FF4998BD}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{7F618648-8E50-4DC0-B288-6CD993840FB4}" name="Column2" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{EF3645F5-0BE4-48DB-B29E-C177BB47CC4C}" name="Column3" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{EB69A2FB-DBB9-4FE5-BED5-8121EF9313B1}" name="Column4" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{FD215D26-D2BF-41DB-B058-CF22763E6EE0}" name="Column5" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{7245048F-85FE-4E7F-B3F5-156C2BE4C803}" name="Column6" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{7F618648-8E50-4DC0-B288-6CD993840FB4}" name="Column2" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{EF3645F5-0BE4-48DB-B29E-C177BB47CC4C}" name="Column3" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{EB69A2FB-DBB9-4FE5-BED5-8121EF9313B1}" name="Column4" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{FD215D26-D2BF-41DB-B058-CF22763E6EE0}" name="Column5" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{7245048F-85FE-4E7F-B3F5-156C2BE4C803}" name="Column6" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{9565D7A7-9C50-40C6-ADD4-AC220B8E1416}" name="Column7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1319,7 +1319,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1503CE6A-6F5B-42CF-B835-8677243A5452}" name="Table1" displayName="Table1" ref="A3:H25" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1503CE6A-6F5B-42CF-B835-8677243A5452}" name="Table1" displayName="Table1" ref="A3:H25" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A3:H25" xr:uid="{1503CE6A-6F5B-42CF-B835-8677243A5452}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:H25">
     <sortCondition ref="B3:B25"/>
@@ -1668,12 +1668,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="50" t="s">
@@ -2068,16 +2068,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
@@ -2355,31 +2355,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="72"/>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
+      <c r="A1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
     </row>
     <row r="5" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -2415,10 +2415,10 @@
       <c r="K5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="U5" s="76" t="s">
+      <c r="U5" s="78" t="s">
         <v>141</v>
       </c>
-      <c r="V5" s="77"/>
+      <c r="V5" s="79"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
@@ -2579,18 +2579,14 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
-      <c r="B12" s="30" t="s">
-        <v>128</v>
-      </c>
+      <c r="B12" s="30"/>
       <c r="C12" s="30"/>
       <c r="D12" s="25"/>
       <c r="E12" s="26"/>
       <c r="F12" s="41"/>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
-      <c r="I12" s="30">
-        <v>1660</v>
-      </c>
+      <c r="I12" s="30"/>
       <c r="J12" s="30"/>
       <c r="K12" s="30"/>
       <c r="U12" s="30"/>
@@ -2763,7 +2759,7 @@
       <c r="N18">
         <v>150</v>
       </c>
-      <c r="O18" s="79">
+      <c r="O18" s="72">
         <v>46192</v>
       </c>
       <c r="U18" s="30" t="s">
@@ -3121,7 +3117,7 @@
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I35" s="23">
         <f>SUM(I7:I34)</f>
-        <v>117329</v>
+        <v>115669</v>
       </c>
       <c r="J35" s="38" t="s">
         <v>188</v>
@@ -3172,15 +3168,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -3682,18 +3678,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
@@ -3719,14 +3715,14 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="75" t="s">
+      <c r="F7" s="76" t="s">
         <v>189</v>
       </c>
-      <c r="G7" s="75"/>
+      <c r="G7" s="76"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
     </row>
     <row r="9" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
@@ -4422,16 +4418,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -5126,12 +5122,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
     </row>
     <row r="3" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -5454,12 +5450,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
     </row>
     <row r="3" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -5936,15 +5932,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="74" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
@@ -6009,11 +6005,11 @@
       </c>
       <c r="E6" s="43">
         <f>SUM(الرواتب!I7:I34)</f>
-        <v>117329</v>
+        <v>115669</v>
       </c>
       <c r="F6" s="43">
         <f>SUM(E22)</f>
-        <v>-67746</v>
+        <v>-66086</v>
       </c>
       <c r="G6" s="44"/>
     </row>
@@ -6038,15 +6034,15 @@
       <c r="B13" s="1"/>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="80">
+      <c r="E17" s="73">
         <f>SUM(C6:E6)</f>
-        <v>310024</v>
+        <v>308364</v>
       </c>
     </row>
     <row r="22" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E22" s="80">
+      <c r="E22" s="73">
         <f>SUM(B6-E17)</f>
-        <v>-67746</v>
+        <v>-66086</v>
       </c>
     </row>
   </sheetData>
@@ -6080,16 +6076,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -6473,15 +6469,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
